--- a/docs/BOM_Comparison.xlsx
+++ b/docs/BOM_Comparison.xlsx
@@ -9,7 +9,8 @@
   </bookViews>
   <sheets>
     <sheet name="단가·기능 비교" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="최초 견적 (참고)" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="카메라·광학" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="최초 견적 (참고)" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="253">
   <si>
     <r>
       <rPr>
@@ -3717,6 +3718,4085 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">안이 유리합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="15"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">카메라 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="15"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="15"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">접사렌즈 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="15"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="15"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">해상도 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="15"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="15"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">표시 배율 정리</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">노란 칸은 입력값입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">값을 바꾸면 아래 배율</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">해상력이 모두 다시 계산됩니다</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">광학 계산 출처</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: docs/scalp-scope.md</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">■ 0. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기준값 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">센서 가로 픽셀 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">px</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC3336 2304×1296</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">센서 유효 폭 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">mm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1/2.8" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">규격 기준</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">센서 유효 폭 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">64MP 1/1.7"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">급 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= 9248px × 0.8μm</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">렌즈 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">값</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SC3336 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모듈 기본 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F2.0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">빛 파장 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">λ</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">μm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가시광 중심</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">녹색</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인치 폰 가로 폭</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인치 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16:9 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가로 방향</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">24</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인치 모니터 가로 폭</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인치 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16:9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">■ 1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">센서 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">카메라 사양</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SC3336</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">64MP</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">급</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">센서</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC3336 (SmartSens)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">64MP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">급 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(GW1 / IMX686 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">계열로 추정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안은 정확한 모델명이 없어 동급 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">64MP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">센서의 일반 제원으로 비교함 — 실제 모델 확인 필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">해상도</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3MP — 2304×1296</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">64MP — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9248×6944</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명목 화소는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배 차이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">센서 크기</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1/2.8" (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">유효 폭 약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.1mm)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1/1.7" (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">유효 폭 약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7.4mm)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">센서가 크면 같은 시야를 담는 데 더 높은 광학 배율이 필요해 접사가 오히려 까다로워짐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">픽셀 피치</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.2μm</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.8μm (4:1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">비닝 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.6μm)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">픽셀이 작을수록 감도가 낮음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">접사는 빛이 급격히 부족해지는 조건이라 불리하게 작용함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">최대 프레임</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30fps @ 3MP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전체 화소</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">센서는 고속이나 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PX30 ISP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8MP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 제한</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PX30·RV1106G3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모두 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ISP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상한이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8MP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">라 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">64MP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">를 실시간으로 처리하지 못함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">렌즈 마운트</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M12 (S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">마운트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">교체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연장 가능</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">스마트폰형 고정 모듈이 일반적 — 확인 필요</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">접사 개조의 핵심</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. M12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 렌즈를 풀어 배율을 올리고 익스텐션 링을 끼울 수 있음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고정 초점 모듈이면 접사 개조가 사실상 불가능하므로 반드시 확인해야 함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">실사용 출력</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2304×1296 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그대로</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저조도 비닝 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16MP → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">스트리밍은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ISP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상한 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8MP</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">64MP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 밝은 곳 정지컷 전용에 가까움</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">■ 2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">접사 렌즈 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안 기준 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시야 폭 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.5mm </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">초점거리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">카탈로그
+화각</t>
+  </si>
+  <si>
+    <t xml:space="preserve">빼야 할
+거리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">나사
+회전 수</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">렌즈</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">~</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">두피
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">작동거리</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">권장</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100°</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0mm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">바퀴</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사용 불가</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">두피에 닿아 조명이 들어가지 않음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">4mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67°</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4mm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">바퀴</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">빠듯함</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">작동거리가 짧아 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LED </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">링 넣기 어려움</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">6mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48°</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11mm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">바퀴</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">가능</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37°</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15mm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">바퀴</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">12mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">★ 권장</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LED </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">링과 경통을 넣을 공간이 확보됨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">25°</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22mm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">44</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">바퀴</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">19mm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">작동거리가 가장 넉넉함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">16mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19°</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29mm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">59</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">바퀴</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">25mm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연장량이 커서 익스텐션 링이 여러 개 필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">※ M12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">나사산은 보통 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10~18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">바퀴가 한계이므로 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8~12mm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">렌즈에는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">익스텐션 링 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15~22mm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 함께 필요합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">판매 페이지의 화각</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(100°, 67° </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">등</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">은 무한대 초점 기준이라 접사로 빼내는 순간 의미가 없어집니다 — 화각이 아니라 초점거리로 고르세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">■ 3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시야 폭별 해상도와 표시 배율 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SC3336 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기준</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">화면 가로
+시야 폭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">픽셀당
+실제 크기</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인치 폰
+표시 배율</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">24</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인치 모니터
+표시 배율</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">렌즈</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">~</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">두피
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(8mm </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">렌즈</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">머리카락
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(70μm)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">실용성</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30mm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이상</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">넓게 훑어보기 좋음</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20mm</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">여유 있음</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15mm</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">★ 권장 — 모공</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모발이 잘 보이고 쓰기 편함</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11mm</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">좋음 — 실용 범위의 아래쪽</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8mm</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">모발 굵기까지 보이나 조명이 어려움</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5mm</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">두피에 닿아 사실상 사용 불가</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">※ "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">몇 배</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 화면 크기에 따라 달라지는 값입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">같은 영상도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인치 폰과 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인치 모니터에서 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배 차이가 납니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시중 두피 진단기의 배율 표기는 모니터 기준이므로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사양을 관리할 때는 배율이 아니라 시야 폭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(mm)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">으로 잡아야 합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">■ 4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실제 해상력 비교 — 시야 폭 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4mm </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조건</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SC3336 (3MP)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">광학 배율</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">센서가 클수록 같은 시야를 담는 데 더 높은 배율이 필요합니다 → 연장량과 조명 부담이 함께 늘어납니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">유효 조리개</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">접사에서는 조리개가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F × (1 + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배율</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 커집니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배율이 높을수록 빛이 급격히 줄고 회절이 심해집니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회절 한계 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">피사체 기준</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">★ 핵심 — 명목 화소는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">선형 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차이지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실제로 구분할 수 있는 크기의 차이는 약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에 불과합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">센서 샘플링</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안은 광학 한계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(4.8μm)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보다 촘촘하게 이미 샘플링하고 있습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안은 약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4.7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배 과샘플링으로 낭비입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">병목</t>
+  </si>
+  <si>
+    <t xml:space="preserve">광학 — 센서는 이미 충분함</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">광학 — 센서는 약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4.7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배 과샘플링</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양쪽 모두 한계를 정하는 것은 렌즈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조명</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">거리 고정이며 화소가 아닙니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">■ 5. 2</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"64MP" </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">표기가 실제로 도달하는 값</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">단계</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">깎이는 이유</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 카탈로그 표기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64MP</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">센서의 명목 최대 화소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">② 저조도 비닝 후</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16MP</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4:1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">비닝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(0.8μm → 1.6μm)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">으로 감도를 확보</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">접사는 빛이 부족해 사실상 이 모드로 동작</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">③ PX30 ISP </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상한</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">8MP</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PX30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ISP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8MP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">까지만 처리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이 위로는 실시간 경로가 없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">④ 실시간 스트리밍</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2MP (1080p)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PX30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H.264 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인코더가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1080p@30fps</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">까지 지원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결론 — 두피 관찰에서 화소는 이미 병목이 아닙니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">권장 조건</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시야 폭 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4mm)</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에서 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안은 픽셀당 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.74μm</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">광학이 만들어낼 수 있는 한계</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">약 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4.8μm)</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보다 촘촘하게 샘플링하고 있습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">즉 지금도 렌즈가 만든 정보를 남김없이 담고 있어서</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">화소를 늘려도 더 보이는 것이 없습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. 64MP</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 올려도 실제 구분 가능한 크기는 약 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15%</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만 좋아지는 반면</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">픽셀이 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.8μm</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 작아져 접사에서 가장 부족한 빛에는 오히려 불리해집니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결과를 가르는 것은 ① </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8~12mm </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">렌즈 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">익스텐션 링</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, ② LED </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">링 조명</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, ③ </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">거리 고정 경통</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, ④ </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">노출</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">화이트밸런스 고정 이 네 가지입니다</t>
     </r>
     <r>
       <rPr>
@@ -4995,12 +9075,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\-#,##0;\-"/>
     <numFmt numFmtId="166" formatCode="[RED]#,##0;[BLUE]\-#,##0;\-"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0#"/>
+    <numFmt numFmtId="168" formatCode="0.0&quot;mm&quot;"/>
+    <numFmt numFmtId="169" formatCode="0.00&quot;μm&quot;"/>
+    <numFmt numFmtId="170" formatCode="0\배"/>
+    <numFmt numFmtId="171" formatCode="0&quot;픽셀&quot;"/>
+    <numFmt numFmtId="172" formatCode="0.00\배"/>
+    <numFmt numFmtId="173" formatCode="\F0.0"/>
+    <numFmt numFmtId="174" formatCode="0.00&quot;μm/픽셀&quot;"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5146,9 +9234,38 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF808080"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <color rgb="FFC00000"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -5159,7 +9276,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5194,6 +9311,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
         <bgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -5274,7 +9397,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="67">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5387,7 +9510,143 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5433,7 +9692,7 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFB4C7DC"/>
-      <rgbColor rgb="FF7F7F7F"/>
+      <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF2CC"/>
@@ -5465,7 +9724,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF7F7F7F"/>
       <rgbColor rgb="FF1F3864"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -6135,6 +10394,1014 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:G58"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+    </row>
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="29"/>
+      <c r="C5" s="30" t="n">
+        <v>2304</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+    </row>
+    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="29"/>
+      <c r="C6" s="30" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="29"/>
+      <c r="C7" s="30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+    </row>
+    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="29"/>
+      <c r="C8" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="31"/>
+      <c r="E8" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+    </row>
+    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="29"/>
+      <c r="C9" s="30" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+    </row>
+    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" s="32"/>
+      <c r="C10" s="30" t="n">
+        <v>132</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+    </row>
+    <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" s="32"/>
+      <c r="C11" s="30" t="n">
+        <v>531</v>
+      </c>
+      <c r="D11" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+    </row>
+    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E15" s="9"/>
+      <c r="F15" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G15" s="11"/>
+    </row>
+    <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="E16" s="9"/>
+      <c r="F16" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G16" s="13"/>
+    </row>
+    <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" s="18"/>
+      <c r="F17" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="G17" s="13"/>
+    </row>
+    <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="C18" s="19"/>
+      <c r="D18" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E18" s="9"/>
+      <c r="F18" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="G18" s="13"/>
+    </row>
+    <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" s="18"/>
+      <c r="F19" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="G19" s="11"/>
+    </row>
+    <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="E20" s="18"/>
+      <c r="F20" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="G20" s="13"/>
+    </row>
+    <row r="21" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="E21" s="18"/>
+      <c r="F21" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G21" s="11"/>
+    </row>
+    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+    </row>
+    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="B25" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="D25" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="E25" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="F25" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="B26" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="C26" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="D26" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E26" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="F26" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="B27" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="C27" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="D27" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="E27" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="F27" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="G27" s="11"/>
+    </row>
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="B28" s="38" t="s">
+        <v>156</v>
+      </c>
+      <c r="C28" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="D28" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="E28" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="F28" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="B29" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="C29" s="38" t="s">
+        <v>163</v>
+      </c>
+      <c r="D29" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="E29" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="F29" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="B30" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="C30" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="D30" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="E30" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="F30" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="B31" s="40"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+    </row>
+    <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+    </row>
+    <row r="34" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="41" t="n">
+        <v>8</v>
+      </c>
+      <c r="B35" s="42" t="n">
+        <f aca="false">A35*1000/$C$5</f>
+        <v>3.47222222222222</v>
+      </c>
+      <c r="C35" s="43" t="n">
+        <f aca="false">$C$10/A35</f>
+        <v>16.5</v>
+      </c>
+      <c r="D35" s="43" t="n">
+        <f aca="false">$C$11/A35</f>
+        <v>66.375</v>
+      </c>
+      <c r="E35" s="34" t="s">
+        <v>182</v>
+      </c>
+      <c r="F35" s="44" t="n">
+        <f aca="false">70/(A35*1000/$C$5)</f>
+        <v>20.16</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="B36" s="42" t="n">
+        <f aca="false">A36*1000/$C$5</f>
+        <v>2.17013888888889</v>
+      </c>
+      <c r="C36" s="43" t="n">
+        <f aca="false">$C$10/A36</f>
+        <v>26.4</v>
+      </c>
+      <c r="D36" s="43" t="n">
+        <f aca="false">$C$11/A36</f>
+        <v>106.2</v>
+      </c>
+      <c r="E36" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="F36" s="44" t="n">
+        <f aca="false">70/(A36*1000/$C$5)</f>
+        <v>32.256</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="B37" s="46" t="n">
+        <f aca="false">A37*1000/$C$5</f>
+        <v>1.73611111111111</v>
+      </c>
+      <c r="C37" s="47" t="n">
+        <f aca="false">$C$10/A37</f>
+        <v>33</v>
+      </c>
+      <c r="D37" s="47" t="n">
+        <f aca="false">$C$11/A37</f>
+        <v>132.75</v>
+      </c>
+      <c r="E37" s="48" t="s">
+        <v>186</v>
+      </c>
+      <c r="F37" s="49" t="n">
+        <f aca="false">70/(A37*1000/$C$5)</f>
+        <v>40.32</v>
+      </c>
+      <c r="G37" s="50" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="B38" s="42" t="n">
+        <f aca="false">A38*1000/$C$5</f>
+        <v>1.30208333333333</v>
+      </c>
+      <c r="C38" s="43" t="n">
+        <f aca="false">$C$10/A38</f>
+        <v>44</v>
+      </c>
+      <c r="D38" s="43" t="n">
+        <f aca="false">$C$11/A38</f>
+        <v>177</v>
+      </c>
+      <c r="E38" s="36" t="s">
+        <v>188</v>
+      </c>
+      <c r="F38" s="44" t="n">
+        <f aca="false">70/(A38*1000/$C$5)</f>
+        <v>53.76</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="B39" s="42" t="n">
+        <f aca="false">A39*1000/$C$5</f>
+        <v>1.08506944444444</v>
+      </c>
+      <c r="C39" s="43" t="n">
+        <f aca="false">$C$10/A39</f>
+        <v>52.8</v>
+      </c>
+      <c r="D39" s="43" t="n">
+        <f aca="false">$C$11/A39</f>
+        <v>212.4</v>
+      </c>
+      <c r="E39" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="F39" s="44" t="n">
+        <f aca="false">70/(A39*1000/$C$5)</f>
+        <v>64.512</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B40" s="42" t="n">
+        <f aca="false">A40*1000/$C$5</f>
+        <v>0.651041666666667</v>
+      </c>
+      <c r="C40" s="43" t="n">
+        <f aca="false">$C$10/A40</f>
+        <v>88</v>
+      </c>
+      <c r="D40" s="43" t="n">
+        <f aca="false">$C$11/A40</f>
+        <v>354</v>
+      </c>
+      <c r="E40" s="36" t="s">
+        <v>192</v>
+      </c>
+      <c r="F40" s="44" t="n">
+        <f aca="false">70/(A40*1000/$C$5)</f>
+        <v>107.52</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="40" t="s">
+        <v>194</v>
+      </c>
+      <c r="B41" s="40"/>
+      <c r="C41" s="40"/>
+      <c r="D41" s="40"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+    </row>
+    <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+    </row>
+    <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E44" s="5"/>
+      <c r="F44" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G44" s="4"/>
+    </row>
+    <row r="45" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="B45" s="51" t="n">
+        <f aca="false">($C$6/4)</f>
+        <v>1.275</v>
+      </c>
+      <c r="C45" s="51"/>
+      <c r="D45" s="52" t="n">
+        <f aca="false">($C$7/4)</f>
+        <v>1.85</v>
+      </c>
+      <c r="E45" s="52"/>
+      <c r="F45" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="G45" s="13"/>
+    </row>
+    <row r="46" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="B46" s="53" t="n">
+        <f aca="false">($C$8*(1+($C$6/4)))</f>
+        <v>4.55</v>
+      </c>
+      <c r="C46" s="53"/>
+      <c r="D46" s="54" t="n">
+        <f aca="false">($C$8*(1+($C$7/4)))</f>
+        <v>5.7</v>
+      </c>
+      <c r="E46" s="54"/>
+      <c r="F46" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="G46" s="13"/>
+    </row>
+    <row r="47" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B47" s="55" t="n">
+        <f aca="false">(1.22*$C$9/(($C$6/4)/(2*($C$8*(1+($C$6/4))))))</f>
+        <v>4.78909803921569</v>
+      </c>
+      <c r="C47" s="55"/>
+      <c r="D47" s="56" t="n">
+        <f aca="false">(1.22*$C$9/(($C$7/4)/(2*($C$8*(1+($C$7/4))))))</f>
+        <v>4.13481081081081</v>
+      </c>
+      <c r="E47" s="56"/>
+      <c r="F47" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="G47" s="13"/>
+    </row>
+    <row r="48" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B48" s="57" t="n">
+        <f aca="false">4*1000/$C$5</f>
+        <v>1.73611111111111</v>
+      </c>
+      <c r="C48" s="57"/>
+      <c r="D48" s="58" t="n">
+        <f aca="false">4*1000/9248</f>
+        <v>0.432525951557093</v>
+      </c>
+      <c r="E48" s="58"/>
+      <c r="F48" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="G48" s="11"/>
+    </row>
+    <row r="49" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B49" s="59" t="s">
+        <v>206</v>
+      </c>
+      <c r="C49" s="59"/>
+      <c r="D49" s="59" t="s">
+        <v>207</v>
+      </c>
+      <c r="E49" s="59"/>
+      <c r="F49" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="G49" s="13"/>
+    </row>
+    <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+    </row>
+    <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+    </row>
+    <row r="53" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="29" t="s">
+        <v>213</v>
+      </c>
+      <c r="B53" s="29"/>
+      <c r="C53" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+    </row>
+    <row r="54" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="29" t="s">
+        <v>216</v>
+      </c>
+      <c r="B54" s="29"/>
+      <c r="C54" s="60" t="s">
+        <v>217</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+    </row>
+    <row r="55" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="B55" s="32"/>
+      <c r="C55" s="60" t="s">
+        <v>220</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+    </row>
+    <row r="56" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="29" t="s">
+        <v>222</v>
+      </c>
+      <c r="B56" s="29"/>
+      <c r="C56" s="61" t="s">
+        <v>223</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E56" s="11"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
+    </row>
+    <row r="58" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="B58" s="27"/>
+      <c r="C58" s="27"/>
+      <c r="D58" s="27"/>
+      <c r="E58" s="27"/>
+      <c r="F58" s="27"/>
+      <c r="G58" s="27"/>
+    </row>
+  </sheetData>
+  <mergeCells count="77">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="D52:G52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="D53:G53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="D54:G54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="D55:G55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="D56:G56"/>
+    <mergeCell ref="A58:G58"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D9"/>
@@ -6146,109 +11413,109 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
+      <c r="A1" s="62" t="s">
+        <v>226</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
     </row>
     <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>80</v>
+      <c r="B3" s="64" t="s">
+        <v>227</v>
+      </c>
+      <c r="C3" s="64" t="s">
+        <v>228</v>
+      </c>
+      <c r="D3" s="63" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="B4" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>84</v>
+      <c r="A4" s="65" t="s">
+        <v>230</v>
+      </c>
+      <c r="B4" s="66" t="s">
+        <v>231</v>
+      </c>
+      <c r="C4" s="66" t="s">
+        <v>232</v>
+      </c>
+      <c r="D4" s="66" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>87</v>
+      <c r="B5" s="66" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" s="66" t="s">
+        <v>235</v>
+      </c>
+      <c r="D5" s="66" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="31" t="s">
-        <v>88</v>
-      </c>
-      <c r="B6" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>91</v>
+      <c r="A6" s="65" t="s">
+        <v>237</v>
+      </c>
+      <c r="B6" s="66" t="s">
+        <v>238</v>
+      </c>
+      <c r="C6" s="66" t="s">
+        <v>239</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="B7" s="32" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>95</v>
+      <c r="A7" s="65" t="s">
+        <v>241</v>
+      </c>
+      <c r="B7" s="66" t="s">
+        <v>242</v>
+      </c>
+      <c r="C7" s="66" t="s">
+        <v>243</v>
+      </c>
+      <c r="D7" s="66" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="31" t="s">
-        <v>96</v>
-      </c>
-      <c r="B8" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>99</v>
+      <c r="A8" s="65" t="s">
+        <v>245</v>
+      </c>
+      <c r="B8" s="66" t="s">
+        <v>246</v>
+      </c>
+      <c r="C8" s="65" t="s">
+        <v>247</v>
+      </c>
+      <c r="D8" s="66" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>102</v>
-      </c>
-      <c r="D9" s="32" t="s">
-        <v>103</v>
+      <c r="A9" s="65" t="s">
+        <v>249</v>
+      </c>
+      <c r="B9" s="65" t="s">
+        <v>250</v>
+      </c>
+      <c r="C9" s="66" t="s">
+        <v>251</v>
+      </c>
+      <c r="D9" s="66" t="s">
+        <v>252</v>
       </c>
     </row>
   </sheetData>

--- a/docs/BOM_Comparison.xlsx
+++ b/docs/BOM_Comparison.xlsx
@@ -10,7 +10,8 @@
   <sheets>
     <sheet name="단가·기능 비교" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="카메라·광학" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="최초 견적 (참고)" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="타사 제품 분석" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="최초 견적 (참고)" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="407">
   <si>
     <r>
       <rPr>
@@ -8914,6 +8915,4677 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">화이트밸런스 고정 이 네 가지입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타사 제품 분석 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PX30 + ISOCELL GW3   |   </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">우리 제품과의 비교</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">노란 칸 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력값</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실측</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제원</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주황 칸 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">역산 추정값</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">값을 바꾸면 아래 지표가 모두 다시 계산됩니다</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">■ 0. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확정 정보</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보드 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rockchip PX30 (2018)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">센서 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Samsung ISOCELL GW3</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">연산</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cortex-A35 ×4 @ 1.5GHz + Mali-G31 MP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">디스플레이 구동을 위한 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">인코더</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H.264 1080p@30 (H.265 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">라이브뷰 상한을 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1080p</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 묶는 지점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">급</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GW3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">64MP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">를 그대로 받지 못함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">메모리 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ OS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">외장 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DDR3·DDR4 + eMMC / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안드로이드 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8.1·9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">외장 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DDR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BOM 34,200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원의 원인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">센서 해상도</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64MP — 9248×6944, 0.7μm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6.5 × 4.9mm (1/1.97").</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">비닝 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인터페이스</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Tetracell 4-in-1 → 16MP / MIPI CSI-2 4-lane</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저조도에서 유효 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.4μm.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">■ 1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력값 — 실측 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제원 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">역산</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">타사 작동거리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">실측값</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타사 광학 배율 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">m</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">배</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">역산 추정 — 작동거리 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10mm + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">폰 렌즈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">f≈5mm</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타사 렌즈 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">값 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">유력</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">폰 카메라 모듈 통상값</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고정 조리개라 조절 불가</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타사 렌즈 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">값 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대안</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">심도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">44μm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에서 역산하면 나오는 값 — 아래 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">번 참고</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GW3 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">픽셀 피치</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">공식 제원</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GW3 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가로 픽셀</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">타사 라이브뷰 가로</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PX30 H.264 1080p </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상한</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안 광학 배율 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">m</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">우리 목표</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안 렌즈 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">값</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SC3336 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모듈 기본 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F2.0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SC3336 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">픽셀 피치</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SC3336 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가로 픽셀</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">스트림 전폭 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(H.265 2304×1296)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">모니터 가로 폭</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">환산에 쓰인 기준 화면</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">■ 2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">성능 지표 — 조리개 가정별 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(★ = </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">유력</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">지표</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타사 ★</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F1.8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타사 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F4.0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F2.0</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">샘플링</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">피사체 위에서 픽셀 하나가 덮는 실제 크기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">작을수록 촘촘합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">접사에서는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F × (1 + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배율</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 커집니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">광학 분해능</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">★ 회절 한계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이보다 작은 것은 화소를 아무리 늘려도 구분되지 않습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">심도</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">허용착란원을 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">픽셀로 둔 값</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">얕을수록 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">나 거리 고정이 필수가 됩니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">라이브뷰 시야</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타사는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1080p</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 잘라낸 폭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2304px </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전폭입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">전체 센서 시야</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타사는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">64MP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정지컷에서만 이 넓이를 씁니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">머리카락 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(70μm)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">굵기 판정에 쓰이는 화면상 두께</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">모니터 환산 배율</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40cm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모니터에 꽉 채웠을 때</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타사의 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">표기가 여기서 나옵니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">⚠ 조리개 불일치 — 제시된 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">광학 분해능 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5μm"</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">과 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">심도 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">44μm"</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">은 동시에 성립하지 않습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">심도 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">44μm</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">은 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F4.0</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에서 나오는 값인데</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, F4.0</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이면 분해능은 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13.6μm</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">반대로 분해능이 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5μm</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이 되려면 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F1.5</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 필요하고</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그때 심도는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15μm </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수준으로 얕아집니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">폰 카메라 모듈은 고정 조리개 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F1.8 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전후이므로 ★</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F1.8 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">열</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">분해능 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6.1μm · </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">심도 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20μm)</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이 실제에 가깝습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">얕은 심도는 타사가 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VCM AF</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">를 넣은 이유이기도 합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">■ 3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타사 라이브뷰가 만들어지는 방식 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가지 가능성 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">미확인</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">방식</t>
+  </si>
+  <si>
+    <t xml:space="preserve">구분 가능 크기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">판정</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">풀해상도 윈도우 크롭</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제시하신 가정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">분해능 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6.1μm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대비 약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배 과샘플링이고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 0.7μm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">픽셀을 비닝 없이 읽어 저조도에 가장 불리합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">비닝 후 윈도우 크롭</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">★ 가장 합리적</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">분해능 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6.1μm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">과 샘플링이 잘 맞고 저조도에도 유리합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이 경우 타사 라이브뷰는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안과 거의 같아집니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전체 시야 다운스케일</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시야는 넓지만 구분 가능 크기가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10μm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대로 뭉개져 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">표기와 맞지 않습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">■ 4. 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자 비교</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타사
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(PX30+GW3)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현재 시제품
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(RV1106)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목표 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(RV1106)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">보드</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PX30 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안드로이드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RV1106 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">리눅스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">RV1106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">센서</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GW3 64MP / 0.7μm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC3336 3MP / 2.2μm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">동일</t>
+  </si>
+  <si>
+    <t xml:space="preserve">인코딩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H.264 1080p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H.265 2304×1296</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">우리가 앞선 부분</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">DDR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">외장</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">내장 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(SIP)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">내장</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">우리가 앞선 부분 — 원가 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">34,200</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원 차이</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">화면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">자체 디스플레이</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폰 앱</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">우리가 앞선 부분 — 원가</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부피</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.65</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배 ※미확정</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">우리가 뒤진 부분 ① — 부품 몇 만원으로 해결</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08μm/px</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5μm/px</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2μm/px</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배율만 올리면 따라잡힘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.07mm (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방식 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">넓음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07mm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안이 오히려 넓음 — 조준이 쉬움</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13μm (F1.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37μm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">★ A</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안이 근소하게 앞섬</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">둘 다 회절 한계에 묶임</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7μm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2μm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안이 더 깊어 거리 고정이 수월함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">AF</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VCM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">내장</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VCM + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">직접 구현</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타사는 심도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20μm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이라 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 필수였음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">조명</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">링 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LED + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">편광</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">동일 구성</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">우리가 뒤진 부분 ② — 부품 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1~2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원으로 해결</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">■ 5. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시사점</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">① 선명도는 우리가 근소 우위</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">둘 다 회절 한계에 묶여 있고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, F1.8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기준 타사 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6.13μm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.37μm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">으로 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안이 오히려 약간 앞섭니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타사가 우위인 것은 정지컷의 넓이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(9.96mm)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이지 선명도가 아닙니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">② 라이브뷰 넓이도 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안이 앞섬</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타사 라이브뷰는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1080p</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 잘라낸 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.07mm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이고 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2304px </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전폭 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.07mm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. 9.96mm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">64MP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정지컷에서만 나오는 값이라 조준 화면과는 다릅니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">③ 우리가 뒤진 것은 두 가지뿐</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배율 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.4 → 1.0 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">렌즈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">익스텐션 링</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조명</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">편광 부재 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">링 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LED + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">편광 필름</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">합쳐서 부품 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3~5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만원 수준이고 지금 바로 가능합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">④ 화소 차이는 거의 의미 없음</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배율 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에서 샘플링 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.2μm/px</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">면 광학 한계 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.37μm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">을 나이퀴스트로 충분히 담습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타사의 나머지 화소는 과샘플링과 정지컷 크롭 여유로 쓰입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">⑤ 설계 사상의 차이</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">타사는 배율을 낮게 두고 작은 픽셀로 당기는 방식이라 렌즈가 단순하고 심도가 깊어집니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다만 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F1.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에서는 심도가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20μm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이라 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VCM AF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 필수가 됩니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안은 배율로 가서 심도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">35μm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">을 확보하므로 거리 고정 경통만으로도 운용이 가능합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확인이 필요한 항목 — ① 타사 렌즈의 실제 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">값</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">분해능</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">심도가 여기서 갈림</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) ② </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">라이브뷰가 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">번의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A·B·C </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중 어느 방식인지 ③ 현재 시제품의 배율 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.4</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 미측정값이므로 자로 시야 폭을 재서 확정 ④ </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SC3336 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">픽셀 피치 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.2μm</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">은 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1/2.8" </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">규격에서 역산한 값이므로 데이터시트로 확인</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. ①②</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 타사 제품을 실측하거나 분해해야 알 수 있고</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, ③④</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 지금 바로 확인 가능합니다</t>
     </r>
     <r>
       <rPr>
@@ -10192,7 +14864,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="12">
+  <numFmts count="16">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\-#,##0;\-"/>
     <numFmt numFmtId="166" formatCode="[RED]#,##0;[BLUE]\-#,##0;\-"/>
@@ -10205,8 +14877,12 @@
     <numFmt numFmtId="173" formatCode="0.00\배"/>
     <numFmt numFmtId="174" formatCode="\F0.0"/>
     <numFmt numFmtId="175" formatCode="0.00&quot;μm/픽셀&quot;"/>
+    <numFmt numFmtId="176" formatCode="0.00&quot;μm/px&quot;"/>
+    <numFmt numFmtId="177" formatCode="\F0.00"/>
+    <numFmt numFmtId="178" formatCode="0.0&quot;μm&quot;"/>
+    <numFmt numFmtId="179" formatCode="0.00&quot;mm&quot;"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -10401,6 +15077,28 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF808080"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF806000"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF806000"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FFC00000"/>
@@ -10409,7 +15107,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -10419,7 +15117,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEDF3FA"/>
-        <bgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -10456,6 +15154,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9D9D9"/>
         <bgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBD5B5"/>
+        <bgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFEDF3FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -10536,7 +15246,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="114">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -10789,6 +15499,190 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="23" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="28" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="177" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="177" fontId="28" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="177" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="28" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="179" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="179" fontId="28" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="179" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="28" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="28" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="179" fontId="20" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="20" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="179" fontId="20" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="20" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -10831,7 +15725,7 @@
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF806000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFB4C7DC"/>
@@ -10854,12 +15748,12 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFEDF3FA"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFF2F2F2"/>
+      <rgbColor rgb="FFFCE4D6"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFCE4D6"/>
+      <rgbColor rgb="FFFBD5B5"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -12646,6 +17540,1158 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:G68"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="32"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="28" t="s">
+        <v>239</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+    </row>
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="63" t="s">
+        <v>244</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E6" s="9"/>
+      <c r="F6" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="G6" s="13"/>
+    </row>
+    <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="63" t="s">
+        <v>248</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E7" s="9"/>
+      <c r="F7" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="G7" s="13"/>
+    </row>
+    <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="64" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="C8" s="18"/>
+      <c r="D8" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E8" s="9"/>
+      <c r="F8" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="G8" s="11"/>
+    </row>
+    <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="63" t="s">
+        <v>253</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="C9" s="18"/>
+      <c r="D9" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E9" s="9"/>
+      <c r="F9" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="G9" s="13"/>
+    </row>
+    <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="63" t="s">
+        <v>256</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="E10" s="9"/>
+      <c r="F10" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="G10" s="13"/>
+    </row>
+    <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="63" t="s">
+        <v>259</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="E11" s="9"/>
+      <c r="F11" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="G11" s="13"/>
+    </row>
+    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="63" t="s">
+        <v>263</v>
+      </c>
+      <c r="B14" s="63"/>
+      <c r="C14" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" s="65" t="s">
+        <v>95</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+    </row>
+    <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="63" t="s">
+        <v>265</v>
+      </c>
+      <c r="B15" s="63"/>
+      <c r="C15" s="66" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D15" s="67" t="s">
+        <v>266</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+    </row>
+    <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="63" t="s">
+        <v>268</v>
+      </c>
+      <c r="B16" s="63"/>
+      <c r="C16" s="66" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D16" s="65"/>
+      <c r="E16" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+    </row>
+    <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="63" t="s">
+        <v>270</v>
+      </c>
+      <c r="B17" s="63"/>
+      <c r="C17" s="66" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" s="65"/>
+      <c r="E17" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+    </row>
+    <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="64" t="s">
+        <v>272</v>
+      </c>
+      <c r="B18" s="64"/>
+      <c r="C18" s="30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D18" s="65" t="s">
+        <v>84</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+    </row>
+    <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="64" t="s">
+        <v>274</v>
+      </c>
+      <c r="B19" s="64"/>
+      <c r="C19" s="30" t="n">
+        <v>9248</v>
+      </c>
+      <c r="D19" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+    </row>
+    <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="63" t="s">
+        <v>275</v>
+      </c>
+      <c r="B20" s="63"/>
+      <c r="C20" s="30" t="n">
+        <v>1920</v>
+      </c>
+      <c r="D20" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+    </row>
+    <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="64" t="s">
+        <v>277</v>
+      </c>
+      <c r="B21" s="64"/>
+      <c r="C21" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="67" t="s">
+        <v>266</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+    </row>
+    <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="64" t="s">
+        <v>279</v>
+      </c>
+      <c r="B22" s="64"/>
+      <c r="C22" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="65"/>
+      <c r="E22" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+    </row>
+    <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="64" t="s">
+        <v>281</v>
+      </c>
+      <c r="B23" s="64"/>
+      <c r="C23" s="66" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D23" s="65" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+    </row>
+    <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="64" t="s">
+        <v>282</v>
+      </c>
+      <c r="B24" s="64"/>
+      <c r="C24" s="30" t="n">
+        <v>2304</v>
+      </c>
+      <c r="D24" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+    </row>
+    <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="63" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" s="63"/>
+      <c r="C25" s="30" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D25" s="65" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+    </row>
+    <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="63" t="s">
+        <v>284</v>
+      </c>
+      <c r="B26" s="63"/>
+      <c r="C26" s="30" t="n">
+        <v>400</v>
+      </c>
+      <c r="D26" s="65" t="s">
+        <v>95</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+    </row>
+    <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+    </row>
+    <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+    </row>
+    <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="63" t="s">
+        <v>291</v>
+      </c>
+      <c r="B30" s="68" t="n">
+        <f aca="false">($C$18/$C$15)</f>
+        <v>1.07692307692308</v>
+      </c>
+      <c r="C30" s="69" t="n">
+        <f aca="false">($C$18/$C$15)</f>
+        <v>1.07692307692308</v>
+      </c>
+      <c r="D30" s="70" t="n">
+        <f aca="false">($C$23/$C$21)</f>
+        <v>2.2</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+    </row>
+    <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="63" t="s">
+        <v>210</v>
+      </c>
+      <c r="B31" s="71" t="n">
+        <f aca="false">($C$16*(1+$C$15))</f>
+        <v>2.97</v>
+      </c>
+      <c r="C31" s="72" t="n">
+        <f aca="false">($C$17*(1+$C$15))</f>
+        <v>6.6</v>
+      </c>
+      <c r="D31" s="73" t="n">
+        <f aca="false">($C$22*(1+$C$21))</f>
+        <v>4</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+    </row>
+    <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="63" t="s">
+        <v>294</v>
+      </c>
+      <c r="B32" s="74" t="n">
+        <f aca="false">(2.44*$C$25*($C$16*(1+$C$15))/$C$15)</f>
+        <v>6.13190769230769</v>
+      </c>
+      <c r="C32" s="75" t="n">
+        <f aca="false">(2.44*$C$25*($C$17*(1+$C$15))/$C$15)</f>
+        <v>13.6264615384615</v>
+      </c>
+      <c r="D32" s="76" t="n">
+        <f aca="false">(2.44*$C$25*($C$22*(1+$C$21))/$C$21)</f>
+        <v>5.368</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+    </row>
+    <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="63" t="s">
+        <v>296</v>
+      </c>
+      <c r="B33" s="77" t="n">
+        <f aca="false">(2*$C$16*(2*$C$18)*(1+$C$15)/$C$15^2)</f>
+        <v>19.6828402366864</v>
+      </c>
+      <c r="C33" s="78" t="n">
+        <f aca="false">(2*$C$17*(2*$C$18)*(1+$C$15)/$C$15^2)</f>
+        <v>43.7396449704142</v>
+      </c>
+      <c r="D33" s="79" t="n">
+        <f aca="false">(2*$C$22*(2*$C$23)*(1+$C$21)/$C$21^2)</f>
+        <v>35.2</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+    </row>
+    <row r="34" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="63" t="s">
+        <v>298</v>
+      </c>
+      <c r="B34" s="80" t="n">
+        <f aca="false">($C$20*$C$18/$C$15/1000)</f>
+        <v>2.06769230769231</v>
+      </c>
+      <c r="C34" s="81" t="n">
+        <f aca="false">($C$20*$C$18/$C$15/1000)</f>
+        <v>2.06769230769231</v>
+      </c>
+      <c r="D34" s="82" t="n">
+        <f aca="false">($C$24*$C$23/$C$21/1000)</f>
+        <v>5.0688</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+    </row>
+    <row r="35" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="63" t="s">
+        <v>300</v>
+      </c>
+      <c r="B35" s="80" t="n">
+        <f aca="false">($C$19*$C$18/$C$15/1000)</f>
+        <v>9.95938461538461</v>
+      </c>
+      <c r="C35" s="81" t="n">
+        <f aca="false">($C$19*$C$18/$C$15/1000)</f>
+        <v>9.95938461538461</v>
+      </c>
+      <c r="D35" s="82" t="n">
+        <f aca="false">($C$24*$C$23/$C$21/1000)</f>
+        <v>5.0688</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+    </row>
+    <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="63" t="s">
+        <v>302</v>
+      </c>
+      <c r="B36" s="83" t="n">
+        <f aca="false">70/($C$18/$C$15)</f>
+        <v>65</v>
+      </c>
+      <c r="C36" s="84" t="n">
+        <f aca="false">70/($C$18/$C$15)</f>
+        <v>65</v>
+      </c>
+      <c r="D36" s="85" t="n">
+        <f aca="false">70/($C$23/$C$21)</f>
+        <v>31.8181818181818</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+    </row>
+    <row r="37" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="63" t="s">
+        <v>304</v>
+      </c>
+      <c r="B37" s="86" t="n">
+        <f aca="false">$C$26/($C$20*$C$18/$C$15/1000)</f>
+        <v>193.452380952381</v>
+      </c>
+      <c r="C37" s="87" t="n">
+        <f aca="false">$C$26/($C$20*$C$18/$C$15/1000)</f>
+        <v>193.452380952381</v>
+      </c>
+      <c r="D37" s="88" t="n">
+        <f aca="false">$C$26/($C$24*$C$23/$C$21/1000)</f>
+        <v>78.9141414141414</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+    </row>
+    <row r="38" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="89" t="s">
+        <v>306</v>
+      </c>
+      <c r="B38" s="89"/>
+      <c r="C38" s="89"/>
+      <c r="D38" s="89"/>
+      <c r="E38" s="89"/>
+      <c r="F38" s="89"/>
+      <c r="G38" s="89"/>
+    </row>
+    <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+    </row>
+    <row r="41" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+    </row>
+    <row r="42" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="64" t="s">
+        <v>311</v>
+      </c>
+      <c r="B42" s="90" t="n">
+        <f aca="false">($C$18/$C$15)</f>
+        <v>1.07692307692308</v>
+      </c>
+      <c r="C42" s="91" t="n">
+        <f aca="false">($C$20*$C$18/$C$15/1000)</f>
+        <v>2.06769230769231</v>
+      </c>
+      <c r="D42" s="92" t="n">
+        <f aca="false">2*($C$18/$C$15)</f>
+        <v>2.15384615384615</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+    </row>
+    <row r="43" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="64" t="s">
+        <v>313</v>
+      </c>
+      <c r="B43" s="93" t="n">
+        <f aca="false">2*$C$18/$C$15</f>
+        <v>2.15384615384615</v>
+      </c>
+      <c r="C43" s="94" t="n">
+        <f aca="false">($C$20*(2*$C$18)/$C$15/1000)</f>
+        <v>4.13538461538462</v>
+      </c>
+      <c r="D43" s="95" t="n">
+        <f aca="false">2*(2*$C$18/$C$15)</f>
+        <v>4.30769230769231</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+    </row>
+    <row r="44" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="64" t="s">
+        <v>315</v>
+      </c>
+      <c r="B44" s="90" t="n">
+        <f aca="false">($C$19*$C$18/$C$15/1000)/$C$20/0.001</f>
+        <v>5.18717948717949</v>
+      </c>
+      <c r="C44" s="91" t="n">
+        <f aca="false">($C$19*$C$18/$C$15/1000)</f>
+        <v>9.95938461538461</v>
+      </c>
+      <c r="D44" s="92" t="n">
+        <f aca="false">2*(($C$19*$C$18/$C$15/1000)/$C$20/0.001)</f>
+        <v>10.374358974359</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+    </row>
+    <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+    </row>
+    <row r="47" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+    </row>
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="63" t="s">
+        <v>321</v>
+      </c>
+      <c r="B48" s="96" t="s">
+        <v>322</v>
+      </c>
+      <c r="C48" s="97" t="s">
+        <v>323</v>
+      </c>
+      <c r="D48" s="98" t="s">
+        <v>324</v>
+      </c>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+    </row>
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="63" t="s">
+        <v>325</v>
+      </c>
+      <c r="B49" s="96" t="s">
+        <v>326</v>
+      </c>
+      <c r="C49" s="97" t="s">
+        <v>327</v>
+      </c>
+      <c r="D49" s="99" t="s">
+        <v>328</v>
+      </c>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+    </row>
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="100" t="s">
+        <v>329</v>
+      </c>
+      <c r="B50" s="101" t="s">
+        <v>330</v>
+      </c>
+      <c r="C50" s="101" t="s">
+        <v>331</v>
+      </c>
+      <c r="D50" s="102" t="s">
+        <v>328</v>
+      </c>
+      <c r="E50" s="103" t="s">
+        <v>332</v>
+      </c>
+      <c r="F50" s="103"/>
+      <c r="G50" s="103"/>
+    </row>
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="104" t="s">
+        <v>333</v>
+      </c>
+      <c r="B51" s="102" t="s">
+        <v>334</v>
+      </c>
+      <c r="C51" s="102" t="s">
+        <v>335</v>
+      </c>
+      <c r="D51" s="102" t="s">
+        <v>336</v>
+      </c>
+      <c r="E51" s="103" t="s">
+        <v>337</v>
+      </c>
+      <c r="F51" s="103"/>
+      <c r="G51" s="103"/>
+    </row>
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="100" t="s">
+        <v>338</v>
+      </c>
+      <c r="B52" s="102" t="s">
+        <v>339</v>
+      </c>
+      <c r="C52" s="102" t="s">
+        <v>340</v>
+      </c>
+      <c r="D52" s="102" t="s">
+        <v>340</v>
+      </c>
+      <c r="E52" s="103" t="s">
+        <v>341</v>
+      </c>
+      <c r="F52" s="103"/>
+      <c r="G52" s="103"/>
+    </row>
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="63" t="s">
+        <v>208</v>
+      </c>
+      <c r="B53" s="96" t="s">
+        <v>342</v>
+      </c>
+      <c r="C53" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="D53" s="98" t="s">
+        <v>344</v>
+      </c>
+      <c r="E53" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+    </row>
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="63" t="s">
+        <v>291</v>
+      </c>
+      <c r="B54" s="96" t="s">
+        <v>346</v>
+      </c>
+      <c r="C54" s="105" t="s">
+        <v>347</v>
+      </c>
+      <c r="D54" s="98" t="s">
+        <v>348</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+    </row>
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="63" t="s">
+        <v>298</v>
+      </c>
+      <c r="B55" s="96" t="s">
+        <v>350</v>
+      </c>
+      <c r="C55" s="105" t="s">
+        <v>351</v>
+      </c>
+      <c r="D55" s="98" t="s">
+        <v>352</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+    </row>
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="100" t="s">
+        <v>294</v>
+      </c>
+      <c r="B56" s="101" t="s">
+        <v>354</v>
+      </c>
+      <c r="C56" s="101" t="s">
+        <v>246</v>
+      </c>
+      <c r="D56" s="101" t="s">
+        <v>355</v>
+      </c>
+      <c r="E56" s="106" t="s">
+        <v>356</v>
+      </c>
+      <c r="F56" s="106"/>
+      <c r="G56" s="106"/>
+    </row>
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="63" t="s">
+        <v>296</v>
+      </c>
+      <c r="B57" s="96" t="s">
+        <v>357</v>
+      </c>
+      <c r="C57" s="97" t="s">
+        <v>246</v>
+      </c>
+      <c r="D57" s="98" t="s">
+        <v>358</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+    </row>
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="64" t="s">
+        <v>360</v>
+      </c>
+      <c r="B58" s="96" t="s">
+        <v>361</v>
+      </c>
+      <c r="C58" s="105" t="s">
+        <v>48</v>
+      </c>
+      <c r="D58" s="98" t="s">
+        <v>362</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+    </row>
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="63" t="s">
+        <v>364</v>
+      </c>
+      <c r="B59" s="107" t="s">
+        <v>365</v>
+      </c>
+      <c r="C59" s="105" t="s">
+        <v>48</v>
+      </c>
+      <c r="D59" s="99" t="s">
+        <v>366</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="F59" s="13"/>
+      <c r="G59" s="13"/>
+    </row>
+    <row r="61" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+    </row>
+    <row r="62" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="108" t="s">
+        <v>369</v>
+      </c>
+      <c r="B62" s="108"/>
+      <c r="C62" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="D62" s="13"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13"/>
+      <c r="G62" s="13"/>
+    </row>
+    <row r="63" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="108" t="s">
+        <v>371</v>
+      </c>
+      <c r="B63" s="108"/>
+      <c r="C63" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="D63" s="13"/>
+      <c r="E63" s="13"/>
+      <c r="F63" s="13"/>
+      <c r="G63" s="13"/>
+    </row>
+    <row r="64" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="108" t="s">
+        <v>373</v>
+      </c>
+      <c r="B64" s="108"/>
+      <c r="C64" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="D64" s="13"/>
+      <c r="E64" s="13"/>
+      <c r="F64" s="13"/>
+      <c r="G64" s="13"/>
+    </row>
+    <row r="65" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="108" t="s">
+        <v>375</v>
+      </c>
+      <c r="B65" s="108"/>
+      <c r="C65" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="13"/>
+    </row>
+    <row r="66" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="108" t="s">
+        <v>377</v>
+      </c>
+      <c r="B66" s="108"/>
+      <c r="C66" s="13" t="s">
+        <v>378</v>
+      </c>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="13"/>
+    </row>
+    <row r="68" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="27" t="s">
+        <v>379</v>
+      </c>
+      <c r="B68" s="27"/>
+      <c r="C68" s="27"/>
+      <c r="D68" s="27"/>
+      <c r="E68" s="27"/>
+      <c r="F68" s="27"/>
+      <c r="G68" s="27"/>
+    </row>
+  </sheetData>
+  <mergeCells count="93">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="E32:G32"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="E42:G42"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="E48:G48"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="E51:G51"/>
+    <mergeCell ref="E52:G52"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="A61:G61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="A68:G68"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D9"/>
@@ -12657,109 +18703,109 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="63" t="s">
-        <v>239</v>
-      </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
+      <c r="A1" s="109" t="s">
+        <v>380</v>
+      </c>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
     </row>
     <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="110" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="65" t="s">
-        <v>240</v>
-      </c>
-      <c r="C3" s="65" t="s">
-        <v>241</v>
-      </c>
-      <c r="D3" s="64" t="s">
-        <v>242</v>
+      <c r="B3" s="111" t="s">
+        <v>381</v>
+      </c>
+      <c r="C3" s="111" t="s">
+        <v>382</v>
+      </c>
+      <c r="D3" s="110" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="66" t="s">
-        <v>243</v>
-      </c>
-      <c r="B4" s="67" t="s">
-        <v>244</v>
-      </c>
-      <c r="C4" s="67" t="s">
-        <v>245</v>
-      </c>
-      <c r="D4" s="67" t="s">
-        <v>246</v>
+      <c r="A4" s="112" t="s">
+        <v>384</v>
+      </c>
+      <c r="B4" s="113" t="s">
+        <v>385</v>
+      </c>
+      <c r="C4" s="113" t="s">
+        <v>386</v>
+      </c>
+      <c r="D4" s="113" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="113" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="67" t="s">
-        <v>247</v>
-      </c>
-      <c r="C5" s="67" t="s">
-        <v>248</v>
-      </c>
-      <c r="D5" s="67" t="s">
-        <v>249</v>
+      <c r="B5" s="113" t="s">
+        <v>388</v>
+      </c>
+      <c r="C5" s="113" t="s">
+        <v>389</v>
+      </c>
+      <c r="D5" s="113" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="66" t="s">
-        <v>250</v>
-      </c>
-      <c r="B6" s="67" t="s">
-        <v>251</v>
-      </c>
-      <c r="C6" s="67" t="s">
-        <v>252</v>
-      </c>
-      <c r="D6" s="66" t="s">
-        <v>253</v>
+      <c r="A6" s="112" t="s">
+        <v>391</v>
+      </c>
+      <c r="B6" s="113" t="s">
+        <v>392</v>
+      </c>
+      <c r="C6" s="113" t="s">
+        <v>393</v>
+      </c>
+      <c r="D6" s="112" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="66" t="s">
-        <v>254</v>
-      </c>
-      <c r="B7" s="67" t="s">
-        <v>255</v>
-      </c>
-      <c r="C7" s="67" t="s">
-        <v>256</v>
-      </c>
-      <c r="D7" s="67" t="s">
-        <v>257</v>
+      <c r="A7" s="112" t="s">
+        <v>395</v>
+      </c>
+      <c r="B7" s="113" t="s">
+        <v>396</v>
+      </c>
+      <c r="C7" s="113" t="s">
+        <v>397</v>
+      </c>
+      <c r="D7" s="113" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="66" t="s">
-        <v>258</v>
-      </c>
-      <c r="B8" s="67" t="s">
-        <v>259</v>
-      </c>
-      <c r="C8" s="66" t="s">
-        <v>260</v>
-      </c>
-      <c r="D8" s="67" t="s">
-        <v>261</v>
+      <c r="A8" s="112" t="s">
+        <v>399</v>
+      </c>
+      <c r="B8" s="113" t="s">
+        <v>400</v>
+      </c>
+      <c r="C8" s="112" t="s">
+        <v>401</v>
+      </c>
+      <c r="D8" s="113" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="66" t="s">
-        <v>262</v>
-      </c>
-      <c r="B9" s="66" t="s">
-        <v>263</v>
-      </c>
-      <c r="C9" s="67" t="s">
-        <v>264</v>
-      </c>
-      <c r="D9" s="67" t="s">
-        <v>265</v>
+      <c r="A9" s="112" t="s">
+        <v>403</v>
+      </c>
+      <c r="B9" s="112" t="s">
+        <v>404</v>
+      </c>
+      <c r="C9" s="113" t="s">
+        <v>405</v>
+      </c>
+      <c r="D9" s="113" t="s">
+        <v>406</v>
       </c>
     </row>
   </sheetData>

--- a/docs/BOM_Comparison.xlsx
+++ b/docs/BOM_Comparison.xlsx
@@ -11,7 +11,8 @@
     <sheet name="단가·기능 비교" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="카메라·광학" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="타사 제품 분석" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="최초 견적 (참고)" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="설계·인증" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="최초 견적 (참고)" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="511">
   <si>
     <r>
       <rPr>
@@ -2622,7 +2623,64 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">조립 공정까지 함께 줄어듦</t>
+      <t xml:space="preserve">조립 공정이 함께 줄고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전기적 검증</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(SI/PI)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">과 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">EMC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방사 시험 부담도 낮아짐</t>
     </r>
     <r>
       <rPr>
@@ -2641,26 +2699,140 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">단가표의 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF404040"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">34,200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF404040"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원은 부품비만 반영한 값이라 실제 원가 차이는 더 큼</t>
+      <t xml:space="preserve">특히 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DDR3-1600</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차 하모닉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2,400MHz)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.4GHz WiFi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대역과 겹쳐 디센스를 일으킬 수 있는데</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안은 이 위험이 근본적으로 작음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자세한 내용은 설계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인증 시트 참고</t>
     </r>
     <r>
       <rPr>
@@ -13586,6 +13758,3792 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">는 지금 바로 확인 가능합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">하드웨어 설계 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인증 관점 비교   </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|   1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SIP </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">내장 메모리  </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs  2</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안 외장 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DDR3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">메모리 내장은 부품비 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">34,200</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원 절감에서 끝나지 않고 기판</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">검증</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인증</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양산까지 영향을 미칩니다</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. 2</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안은 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">32</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">비트 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DDR3 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">버스</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(H5TQ4G63EFR ×2 = 1GB) </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기준입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">■ 1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기판</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(PCB) </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">설계</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SIP </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">내장</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안 — 외장 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DDR3 32bit</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">배선해야 할 신호</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">90</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 이상 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(DQ 32 + DQS 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">쌍 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ DM 4 + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">커맨드 약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16 + CK/CKE/CS/ODT)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DDR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">버스는 전부 길이 정합</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(length matching)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">과 임피던스 제어 대상입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">배선 제약</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해당 없음</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40~50Ω · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차동 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">80~100Ω </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">임피던스 제어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, fly-by </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">또는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">T </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">토폴로지 결정</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">층 구성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">스택업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이 임피던스에 묶여 자유도가 크게 줄어듭니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">기판 층수</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">층 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조건에 따라 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">층도 가능</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실무상 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">층 이상 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">최소 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">층</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">★ 기판 단가는 층수에 거의 비례합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부품비와 별개로 발생하는 직접 원가 차이입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일반론 — 실제 층수는 최종 배치에 따라 확정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">기판 면적</t>
+  </si>
+  <si>
+    <t xml:space="preserve">작음</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DRAM 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">종단 저항 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">디커플링 캡 수십 개만큼 추가</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">면적은 기판 단가와 케이스 크기에 함께 영향을 줍니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">■ 2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전기적 검증 공수 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(SI / PI)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안 — 외장 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DDR3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">신호 무결성 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(SI)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">칩 제조사가 검증 완료 — 설계자가 할 일 없음</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시뮬레이션</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아이 다이어그램 검증</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, DDR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">트레이닝 마진 확인 필요</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">★ 외부 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DDR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 온도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전압</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양산 편차에 따라 트레이닝이 실패할 수 있어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">코너 조건까지 확인해야 합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전원 무결성 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(PI)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">코어 전원만 관리</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DDR3L 1.35V </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">레일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ VTT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">종단 전원 추가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">디커플링 캡 수십 개</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전원 레일이 늘면 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PMIC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">채널과 인덕터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">캡이 함께 늘어납니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">디버깅 리스크</t>
+  </si>
+  <si>
+    <t xml:space="preserve">낮음 — 메모리는 이미 동작이 보장된 상태에서 시작</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">높음 — 초기 부팅 불가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">간헐적 행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(hang)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 원인이 메모리인지 판별하는 데 시간이 소요</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시제품 단계에서 일정 리스크로 직결되는 항목입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">■ 3. EMC · </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인증 시험</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">방사 노이즈원</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">패키지 내부 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배선 길이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">mm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단위</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기판 위 배선 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">길이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">cm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단위</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">★ 방사량은 배선 길이와 루프 면적에 비례합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. SIP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 이 안테나 역할을 하는 배선이 패키지 안에 갇혀 있어 기판 밖으로 나가는 방사가 크게 줄어듭니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">KC / CE / FCC </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방사 시험</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">통과 여유가 큼</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DDR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">클럭 하모닉이 주요 탈락 원인 중 하나</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">탈락 시 차폐캔 추가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">스펙트럼 확산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">재설계 후 재시험이 필요해 비용과 일정이 함께 늘어납니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">대응 수단</t>
+  </si>
+  <si>
+    <t xml:space="preserve">특별한 대응 불필요</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차폐캔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">스펙트럼 확산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(SSC), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">클럭 주파수 조정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배치 분리</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모두 원가나 성능을 대가로 지불하는 수단입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">전도 노이즈</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전원 레일이 단순해 유리</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DDR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전원 레일의 스위칭 전류가 추가됨</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">⚠ 정확히 하자면 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SIP</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 노이즈를 없애는 것은 아닙니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. DRAM </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다이는 여전히 스위칭하고 전류를 끌어씁니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다만 방사의 주된 원인은 기판 위를 지나는 긴 배선이고</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, SIP</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 그 배선을 패키지 안 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">mm </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단위로 가둡니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. "</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">없어진다</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 아니라 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">크게 줄고</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">설계자가 관리할 대상에서 빠진다</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 정확한 표현입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">■ 4. WiFi </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공존 — 이 제품에 직접 영향</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.4GHz </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대역</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">~</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MHz</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ISM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대역 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력값</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DDR3 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">등급</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">클럭</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.4GHz </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대역 충돌</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">DDR3-1066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDR3-1333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDR3-1600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDR3-1866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDR3-2133</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">★ DDR3-1600</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">은 클럭 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">800MHz</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차 하모닉이 정확히 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2,400MHz</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 2.4GHz WiFi </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대역의 시작점과 겹칩니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이 노이즈가 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">WiFi </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수신기의 바닥 잡음을 끌어올리면 수신 감도가 떨어지는 디센스</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(desense)</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 생기고</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실사용에서는 전송 거리 단축과 스트리밍 끊김으로 나타납니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이 제품은 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">WiFi </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실시간 스트리밍이 핵심 기능이므로 성능에 직결됩니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF806000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">디센스 위험</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">근본적으로 낮음 — 기판에 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DDR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배선 자체가 없음</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">설계로 풀어야 함 — 클럭 조정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, SSC, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차폐캔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배선 분리</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안은 외장 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DDR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">와 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">WiFi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모듈이 같은 기판에 놓이므로 배치 단계부터 고려가 필요합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">영향</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전송 거리 단축</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">스트리밍 끊김</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">재전송 증가에 따른 지연 상승</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">증상이 간헐적이라 원인 규명이 어렵고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양산 후 발견되면 대응 비용이 큽니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">■ 5. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">양산 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">검사</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">실장 공정</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DRAM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실장 공정 없음</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BGA 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 실장 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">납땜 품질 관리</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BGA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 육안 검사가 불가능해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">X-ray </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">검사 공정이 필요합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">불량 요인</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">납땜 보이드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">냉납</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">미실장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방향 오조립</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부품 수가 늘수록 실장 불량률이 함께 올라갑니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">검사 공정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메모리 테스트 불필요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메모리 동작 테스트 공정 추가</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공정 시간이 늘면 대당 가공비가 올라갑니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">신뢰성</t>
+  </si>
+  <si>
+    <t xml:space="preserve">부품 수가 적어 유리</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DRAM 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수동소자 수십 개 추가</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부품 수 감소는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MTBF </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개선으로 이어집니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">■ 6. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">요약 — 부품비 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">34,200</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원 밖에서 생기는 차이</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">직접 원가</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기판 층수 감소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">층 → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">층</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기판 면적 감소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, DRAM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">검사 공정 제거</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">개발 일정</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DDR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배선 설계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·SI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시뮬레이션</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">트레이닝 검증 공수가 통째로 사라짐</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">인증 리스크</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">EMC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방사 시험의 주요 탈락 원인 하나가 제거되어 재시험 위험이 낮아짐</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">제품 성능</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">★ 2.4GHz WiFi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">디센스 위험이 근본적으로 낮음 — 스트리밍 거리와 안정성에 직결</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">양산 품질</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BGA </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실장 불량 요인 제거</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">부품 수 감소로 신뢰성 향상</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정리 — 단가표의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">34,200</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원은 부품비만 반영한 값입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실제로는 기판 층수</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">면적</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">설계와 검증 공수</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, EMC </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인증 리스크</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실장</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">검사 공정</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그리고 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">WiFi </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">성능까지 함께 따라옵니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원가만 놓고 봐도 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">34,200</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원보다 크고</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개발 일정과 제품 성능에서 얻는 이득은 여기에 포함되지 않은 몫입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다만 층수와 공정비는 최종 배치와 협력사 견적에 따라 달라지므로</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">확정 수치는 기구</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F3864"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기판 설계가 나온 뒤에 채워야 합니다</t>
     </r>
     <r>
       <rPr>
@@ -14864,7 +18822,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="16">
+  <numFmts count="17">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\-#,##0;\-"/>
     <numFmt numFmtId="166" formatCode="[RED]#,##0;[BLUE]\-#,##0;\-"/>
@@ -14881,6 +18839,7 @@
     <numFmt numFmtId="177" formatCode="\F0.00"/>
     <numFmt numFmtId="178" formatCode="0.0&quot;μm&quot;"/>
     <numFmt numFmtId="179" formatCode="0.00&quot;mm&quot;"/>
+    <numFmt numFmtId="180" formatCode="0&quot;MHz&quot;"/>
   </numFmts>
   <fonts count="32">
     <font>
@@ -15246,7 +19205,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="122">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -15683,6 +19642,38 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="180" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="180" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="180" fontId="31" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -18692,6 +22683,863 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="30"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="28" t="s">
+        <v>380</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+    </row>
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="19"/>
+      <c r="D6" s="18" t="s">
+        <v>386</v>
+      </c>
+      <c r="E6" s="18"/>
+      <c r="F6" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="G6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>389</v>
+      </c>
+      <c r="C7" s="19"/>
+      <c r="D7" s="18" t="s">
+        <v>390</v>
+      </c>
+      <c r="E7" s="18"/>
+      <c r="F7" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="G7" s="13"/>
+    </row>
+    <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="18" t="s">
+        <v>394</v>
+      </c>
+      <c r="E8" s="18"/>
+      <c r="F8" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="G8" s="13"/>
+    </row>
+    <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>397</v>
+      </c>
+      <c r="C9" s="19"/>
+      <c r="D9" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="E9" s="9"/>
+      <c r="F9" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="G9" s="13"/>
+    </row>
+    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="C13" s="19"/>
+      <c r="D13" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="E13" s="9"/>
+      <c r="F13" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="G13" s="13"/>
+    </row>
+    <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>407</v>
+      </c>
+      <c r="C14" s="19"/>
+      <c r="D14" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="E14" s="9"/>
+      <c r="F14" s="13" t="s">
+        <v>409</v>
+      </c>
+      <c r="G14" s="13"/>
+    </row>
+    <row r="15" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="E15" s="18"/>
+      <c r="F15" s="13" t="s">
+        <v>413</v>
+      </c>
+      <c r="G15" s="13"/>
+    </row>
+    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+    </row>
+    <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C19" s="19"/>
+      <c r="D19" s="18" t="s">
+        <v>417</v>
+      </c>
+      <c r="E19" s="18"/>
+      <c r="F19" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="G19" s="13"/>
+    </row>
+    <row r="20" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>420</v>
+      </c>
+      <c r="C20" s="19"/>
+      <c r="D20" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="E20" s="9"/>
+      <c r="F20" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="G20" s="13"/>
+    </row>
+    <row r="21" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>424</v>
+      </c>
+      <c r="C21" s="19"/>
+      <c r="D21" s="18" t="s">
+        <v>425</v>
+      </c>
+      <c r="E21" s="18"/>
+      <c r="F21" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="G21" s="13"/>
+    </row>
+    <row r="22" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="C22" s="19"/>
+      <c r="D22" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="E22" s="9"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+    </row>
+    <row r="23" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="89" t="s">
+        <v>430</v>
+      </c>
+      <c r="B23" s="89"/>
+      <c r="C23" s="89"/>
+      <c r="D23" s="89"/>
+      <c r="E23" s="89"/>
+      <c r="F23" s="89"/>
+      <c r="G23" s="89"/>
+    </row>
+    <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+    </row>
+    <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="109" t="s">
+        <v>432</v>
+      </c>
+      <c r="B26" s="110" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>433</v>
+      </c>
+      <c r="D26" s="110" t="n">
+        <v>2483.5</v>
+      </c>
+      <c r="E26" s="35" t="s">
+        <v>434</v>
+      </c>
+      <c r="F26" s="111" t="s">
+        <v>435</v>
+      </c>
+      <c r="G26" s="111"/>
+    </row>
+    <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="109" t="s">
+        <v>443</v>
+      </c>
+      <c r="B28" s="112" t="n">
+        <v>533</v>
+      </c>
+      <c r="C28" s="112" t="n">
+        <f aca="false">$B$28*2</f>
+        <v>1066</v>
+      </c>
+      <c r="D28" s="112" t="n">
+        <f aca="false">$B$28*3</f>
+        <v>1599</v>
+      </c>
+      <c r="E28" s="112" t="n">
+        <f aca="false">$B$28*4</f>
+        <v>2132</v>
+      </c>
+      <c r="F28" s="112" t="n">
+        <f aca="false">$B$28*5</f>
+        <v>2665</v>
+      </c>
+      <c r="G28" s="35" t="str">
+        <f aca="false">IF(OR(AND(C28&gt;=$B$26,C28&lt;=$D$26),AND(D28&gt;=$B$26,D28&lt;=$D$26),AND(E28&gt;=$B$26,E28&lt;=$D$26),AND(F28&gt;=$B$26,F28&lt;=$D$26)),"★ 충돌","-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="109" t="s">
+        <v>444</v>
+      </c>
+      <c r="B29" s="112" t="n">
+        <v>666.5</v>
+      </c>
+      <c r="C29" s="112" t="n">
+        <f aca="false">$B$29*2</f>
+        <v>1333</v>
+      </c>
+      <c r="D29" s="112" t="n">
+        <f aca="false">$B$29*3</f>
+        <v>1999.5</v>
+      </c>
+      <c r="E29" s="112" t="n">
+        <f aca="false">$B$29*4</f>
+        <v>2666</v>
+      </c>
+      <c r="F29" s="112" t="n">
+        <f aca="false">$B$29*5</f>
+        <v>3332.5</v>
+      </c>
+      <c r="G29" s="35" t="str">
+        <f aca="false">IF(OR(AND(C29&gt;=$B$26,C29&lt;=$D$26),AND(D29&gt;=$B$26,D29&lt;=$D$26),AND(E29&gt;=$B$26,E29&lt;=$D$26),AND(F29&gt;=$B$26,F29&lt;=$D$26)),"★ 충돌","-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="113" t="s">
+        <v>445</v>
+      </c>
+      <c r="B30" s="114" t="n">
+        <v>800</v>
+      </c>
+      <c r="C30" s="114" t="n">
+        <f aca="false">$B$30*2</f>
+        <v>1600</v>
+      </c>
+      <c r="D30" s="115" t="n">
+        <f aca="false">$B$30*3</f>
+        <v>2400</v>
+      </c>
+      <c r="E30" s="114" t="n">
+        <f aca="false">$B$30*4</f>
+        <v>3200</v>
+      </c>
+      <c r="F30" s="114" t="n">
+        <f aca="false">$B$30*5</f>
+        <v>4000</v>
+      </c>
+      <c r="G30" s="40" t="str">
+        <f aca="false">IF(OR(AND(C30&gt;=$B$26,C30&lt;=$D$26),AND(D30&gt;=$B$26,D30&lt;=$D$26),AND(E30&gt;=$B$26,E30&lt;=$D$26),AND(F30&gt;=$B$26,F30&lt;=$D$26)),"★ 충돌","-")</f>
+        <v>★ 충돌</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="109" t="s">
+        <v>446</v>
+      </c>
+      <c r="B31" s="112" t="n">
+        <v>933</v>
+      </c>
+      <c r="C31" s="112" t="n">
+        <f aca="false">$B$31*2</f>
+        <v>1866</v>
+      </c>
+      <c r="D31" s="112" t="n">
+        <f aca="false">$B$31*3</f>
+        <v>2799</v>
+      </c>
+      <c r="E31" s="112" t="n">
+        <f aca="false">$B$31*4</f>
+        <v>3732</v>
+      </c>
+      <c r="F31" s="112" t="n">
+        <f aca="false">$B$31*5</f>
+        <v>4665</v>
+      </c>
+      <c r="G31" s="35" t="str">
+        <f aca="false">IF(OR(AND(C31&gt;=$B$26,C31&lt;=$D$26),AND(D31&gt;=$B$26,D31&lt;=$D$26),AND(E31&gt;=$B$26,E31&lt;=$D$26),AND(F31&gt;=$B$26,F31&lt;=$D$26)),"★ 충돌","-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="109" t="s">
+        <v>447</v>
+      </c>
+      <c r="B32" s="112" t="n">
+        <v>1066.5</v>
+      </c>
+      <c r="C32" s="112" t="n">
+        <f aca="false">$B$32*2</f>
+        <v>2133</v>
+      </c>
+      <c r="D32" s="112" t="n">
+        <f aca="false">$B$32*3</f>
+        <v>3199.5</v>
+      </c>
+      <c r="E32" s="112" t="n">
+        <f aca="false">$B$32*4</f>
+        <v>4266</v>
+      </c>
+      <c r="F32" s="112" t="n">
+        <f aca="false">$B$32*5</f>
+        <v>5332.5</v>
+      </c>
+      <c r="G32" s="35" t="str">
+        <f aca="false">IF(OR(AND(C32&gt;=$B$26,C32&lt;=$D$26),AND(D32&gt;=$B$26,D32&lt;=$D$26),AND(E32&gt;=$B$26,E32&lt;=$D$26),AND(F32&gt;=$B$26,F32&lt;=$D$26)),"★ 충돌","-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="116" t="s">
+        <v>448</v>
+      </c>
+      <c r="B33" s="116"/>
+      <c r="C33" s="116"/>
+      <c r="D33" s="116"/>
+      <c r="E33" s="116"/>
+      <c r="F33" s="116"/>
+      <c r="G33" s="116"/>
+    </row>
+    <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="E35" s="5"/>
+      <c r="F35" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G35" s="4"/>
+    </row>
+    <row r="36" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>450</v>
+      </c>
+      <c r="C36" s="19"/>
+      <c r="D36" s="18" t="s">
+        <v>451</v>
+      </c>
+      <c r="E36" s="18"/>
+      <c r="F36" s="11" t="s">
+        <v>452</v>
+      </c>
+      <c r="G36" s="11"/>
+    </row>
+    <row r="37" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>389</v>
+      </c>
+      <c r="C37" s="19"/>
+      <c r="D37" s="18" t="s">
+        <v>454</v>
+      </c>
+      <c r="E37" s="18"/>
+      <c r="F37" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="G37" s="13"/>
+    </row>
+    <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+    </row>
+    <row r="40" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="E40" s="5"/>
+      <c r="F40" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G40" s="4"/>
+    </row>
+    <row r="41" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="C41" s="7"/>
+      <c r="D41" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="E41" s="9"/>
+      <c r="F41" s="11" t="s">
+        <v>460</v>
+      </c>
+      <c r="G41" s="11"/>
+    </row>
+    <row r="42" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>389</v>
+      </c>
+      <c r="C42" s="19"/>
+      <c r="D42" s="18" t="s">
+        <v>462</v>
+      </c>
+      <c r="E42" s="18"/>
+      <c r="F42" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="G42" s="13"/>
+    </row>
+    <row r="43" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>465</v>
+      </c>
+      <c r="C43" s="19"/>
+      <c r="D43" s="18" t="s">
+        <v>466</v>
+      </c>
+      <c r="E43" s="18"/>
+      <c r="F43" s="13" t="s">
+        <v>467</v>
+      </c>
+      <c r="G43" s="13"/>
+    </row>
+    <row r="44" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>469</v>
+      </c>
+      <c r="C44" s="19"/>
+      <c r="D44" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="E44" s="9"/>
+      <c r="F44" s="13" t="s">
+        <v>471</v>
+      </c>
+      <c r="G44" s="13"/>
+    </row>
+    <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+    </row>
+    <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="108" t="s">
+        <v>473</v>
+      </c>
+      <c r="B47" s="108"/>
+      <c r="C47" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="D47" s="13"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+    </row>
+    <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="108" t="s">
+        <v>475</v>
+      </c>
+      <c r="B48" s="108"/>
+      <c r="C48" s="11" t="s">
+        <v>476</v>
+      </c>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+    </row>
+    <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="108" t="s">
+        <v>477</v>
+      </c>
+      <c r="B49" s="108"/>
+      <c r="C49" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+    </row>
+    <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="108" t="s">
+        <v>479</v>
+      </c>
+      <c r="B50" s="108"/>
+      <c r="C50" s="11" t="s">
+        <v>480</v>
+      </c>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+    </row>
+    <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="108" t="s">
+        <v>481</v>
+      </c>
+      <c r="B51" s="108"/>
+      <c r="C51" s="11" t="s">
+        <v>482</v>
+      </c>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+    </row>
+    <row r="53" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="27" t="s">
+        <v>483</v>
+      </c>
+      <c r="B53" s="27"/>
+      <c r="C53" s="27"/>
+      <c r="D53" s="27"/>
+      <c r="E53" s="27"/>
+      <c r="F53" s="27"/>
+      <c r="G53" s="27"/>
+    </row>
+  </sheetData>
+  <mergeCells count="88">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="A53:G53"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D9"/>
@@ -18703,109 +23551,109 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="109" t="s">
-        <v>380</v>
-      </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
+      <c r="A1" s="117" t="s">
+        <v>484</v>
+      </c>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
     </row>
     <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="110" t="s">
+      <c r="A3" s="118" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="111" t="s">
-        <v>381</v>
-      </c>
-      <c r="C3" s="111" t="s">
-        <v>382</v>
-      </c>
-      <c r="D3" s="110" t="s">
-        <v>383</v>
+      <c r="B3" s="119" t="s">
+        <v>485</v>
+      </c>
+      <c r="C3" s="119" t="s">
+        <v>486</v>
+      </c>
+      <c r="D3" s="118" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="112" t="s">
-        <v>384</v>
-      </c>
-      <c r="B4" s="113" t="s">
-        <v>385</v>
-      </c>
-      <c r="C4" s="113" t="s">
-        <v>386</v>
-      </c>
-      <c r="D4" s="113" t="s">
-        <v>387</v>
+      <c r="A4" s="120" t="s">
+        <v>488</v>
+      </c>
+      <c r="B4" s="121" t="s">
+        <v>489</v>
+      </c>
+      <c r="C4" s="121" t="s">
+        <v>490</v>
+      </c>
+      <c r="D4" s="121" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="113" t="s">
+      <c r="A5" s="121" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="113" t="s">
-        <v>388</v>
-      </c>
-      <c r="C5" s="113" t="s">
-        <v>389</v>
-      </c>
-      <c r="D5" s="113" t="s">
-        <v>390</v>
+      <c r="B5" s="121" t="s">
+        <v>492</v>
+      </c>
+      <c r="C5" s="121" t="s">
+        <v>493</v>
+      </c>
+      <c r="D5" s="121" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="112" t="s">
-        <v>391</v>
-      </c>
-      <c r="B6" s="113" t="s">
-        <v>392</v>
-      </c>
-      <c r="C6" s="113" t="s">
-        <v>393</v>
-      </c>
-      <c r="D6" s="112" t="s">
-        <v>394</v>
+      <c r="A6" s="120" t="s">
+        <v>495</v>
+      </c>
+      <c r="B6" s="121" t="s">
+        <v>496</v>
+      </c>
+      <c r="C6" s="121" t="s">
+        <v>497</v>
+      </c>
+      <c r="D6" s="120" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="112" t="s">
-        <v>395</v>
-      </c>
-      <c r="B7" s="113" t="s">
-        <v>396</v>
-      </c>
-      <c r="C7" s="113" t="s">
-        <v>397</v>
-      </c>
-      <c r="D7" s="113" t="s">
-        <v>398</v>
+      <c r="A7" s="120" t="s">
+        <v>499</v>
+      </c>
+      <c r="B7" s="121" t="s">
+        <v>500</v>
+      </c>
+      <c r="C7" s="121" t="s">
+        <v>501</v>
+      </c>
+      <c r="D7" s="121" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="112" t="s">
-        <v>399</v>
-      </c>
-      <c r="B8" s="113" t="s">
-        <v>400</v>
-      </c>
-      <c r="C8" s="112" t="s">
-        <v>401</v>
-      </c>
-      <c r="D8" s="113" t="s">
-        <v>402</v>
+      <c r="A8" s="120" t="s">
+        <v>503</v>
+      </c>
+      <c r="B8" s="121" t="s">
+        <v>504</v>
+      </c>
+      <c r="C8" s="120" t="s">
+        <v>505</v>
+      </c>
+      <c r="D8" s="121" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="112" t="s">
-        <v>403</v>
-      </c>
-      <c r="B9" s="112" t="s">
-        <v>404</v>
-      </c>
-      <c r="C9" s="113" t="s">
-        <v>405</v>
-      </c>
-      <c r="D9" s="113" t="s">
-        <v>406</v>
+      <c r="A9" s="120" t="s">
+        <v>507</v>
+      </c>
+      <c r="B9" s="120" t="s">
+        <v>508</v>
+      </c>
+      <c r="C9" s="121" t="s">
+        <v>509</v>
+      </c>
+      <c r="D9" s="121" t="s">
+        <v>510</v>
       </c>
     </row>
   </sheetData>

--- a/docs/BOM_Comparison.xlsx
+++ b/docs/BOM_Comparison.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="515">
   <si>
     <r>
       <rPr>
@@ -1709,6 +1709,337 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">. (docs/scalp-scope.md)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">초점</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고정 초점</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자동초점 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(VCM)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">거리 고정 경통을 쓰면 피사체 거리가 항상 같아 두피 스코프에서는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 필수는 아님</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">오히려 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 촬영마다 초점 위치가 달라져 배율이 미세하게 변하므로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">같은 부위를 시간 간격을 두고 비교할 때 스케일이 흔들림 — 두피 관찰의 주 용도가 변화 추적이라 불리하게 작용함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다만 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안의 심도는 약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">35μm(F2.0·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배율 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.0)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 얕아 누르는 압력이나 두피 곡률로 거리가 흔들리면 초점이 빠질 수 있으므로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">경통 제작 후 실측 검증이 필요함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">를 넣은 것은 심도가 약 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20μm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 더 얕아 고정만으로는 감당하기 어려웠기 때문으로 보임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. VCM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">은 부품비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">드라이버 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IC·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구현 공수도 함께 발생함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
   </si>
   <si>
@@ -19946,7 +20277,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -20163,7 +20494,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
         <v>38</v>
       </c>
@@ -20183,31 +20514,31 @@
       <c r="A17" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="9" t="s">
+      <c r="C17" s="19"/>
+      <c r="D17" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="11" t="s">
+      <c r="E17" s="18"/>
+      <c r="F17" s="13" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="6" t="s">
         <v>46</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C18" s="7"/>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="18"/>
-      <c r="F18" s="13" t="s">
+      <c r="E18" s="9"/>
+      <c r="F18" s="11" t="s">
         <v>49</v>
       </c>
     </row>
@@ -20219,10 +20550,10 @@
         <v>51</v>
       </c>
       <c r="C19" s="7"/>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="9"/>
+      <c r="E19" s="18"/>
       <c r="F19" s="13" t="s">
         <v>53</v>
       </c>
@@ -20244,18 +20575,18 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="12" t="s">
         <v>58</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>59</v>
       </c>
       <c r="C21" s="7"/>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E21" s="18"/>
-      <c r="F21" s="11" t="s">
+      <c r="E21" s="9"/>
+      <c r="F21" s="13" t="s">
         <v>61</v>
       </c>
     </row>
@@ -20268,110 +20599,126 @@
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="18" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="E22" s="18"/>
-      <c r="F22" s="13" t="s">
-        <v>64</v>
+      <c r="F22" s="11" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B23" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="19"/>
+      <c r="B23" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="7"/>
       <c r="D23" s="18" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="E23" s="18"/>
       <c r="F23" s="13" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
+    <row r="24" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
+      <c r="B24" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="18"/>
+      <c r="F24" s="13" t="s">
+        <v>72</v>
+      </c>
     </row>
-    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="20" t="s">
+    <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+    </row>
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" s="20" t="s">
+      <c r="B27" s="20"/>
+      <c r="C27" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-    </row>
-    <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="22" t="n">
-        <f aca="false">C10</f>
-        <v>39000</v>
-      </c>
-      <c r="D27" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B28" s="21"/>
       <c r="C28" s="22" t="n">
-        <f aca="false">E10</f>
-        <v>74580</v>
+        <f aca="false">C10</f>
+        <v>39000</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E28" s="23"/>
       <c r="F28" s="23"/>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="B29" s="24"/>
-      <c r="C29" s="25" t="n">
+      <c r="A29" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29" s="21"/>
+      <c r="C29" s="22" t="n">
+        <f aca="false">E10</f>
+        <v>74580</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+    </row>
+    <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" s="24"/>
+      <c r="C30" s="25" t="n">
         <f aca="false">E10-C10</f>
         <v>35580</v>
       </c>
-      <c r="D29" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
+      <c r="D30" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
     </row>
-    <row r="31" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
+    <row r="32" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" s="27"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="38">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
@@ -20398,16 +20745,18 @@
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="D23:E23"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="D27:F27"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="D28:F28"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="D29:F29"/>
-    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="A32:F32"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -20436,7 +20785,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -20447,7 +20796,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -20458,7 +20807,7 @@
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -20469,75 +20818,75 @@
     </row>
     <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="29" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B5" s="29"/>
       <c r="C5" s="30" t="n">
         <v>2304</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="29" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B6" s="29"/>
       <c r="C6" s="30" t="n">
         <v>2.2</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="29" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B7" s="29"/>
       <c r="C7" s="30" t="n">
         <v>9248</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
     </row>
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="29" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B8" s="29"/>
       <c r="C8" s="30" t="n">
         <v>0.7</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
     </row>
     <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B9" s="32"/>
       <c r="C9" s="30" t="n">
@@ -20545,65 +20894,65 @@
       </c>
       <c r="D9" s="31"/>
       <c r="E9" s="11" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B10" s="32"/>
       <c r="C10" s="30" t="n">
         <v>0.55</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="29" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B11" s="29"/>
       <c r="C11" s="30" t="n">
         <v>132</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
     </row>
     <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="29" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B12" s="29"/>
       <c r="C12" s="30" t="n">
         <v>531</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
     </row>
     <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="29" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B13" s="29"/>
       <c r="C13" s="33" t="n">
@@ -20611,17 +20960,17 @@
         <v>5.0688</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
     </row>
     <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="29" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B14" s="29"/>
       <c r="C14" s="33" t="n">
@@ -20629,17 +20978,17 @@
         <v>6.4736</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F14" s="13"/>
       <c r="G14" s="13"/>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -20653,11 +21002,11 @@
         <v>27</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="4" t="s">
@@ -20667,143 +21016,143 @@
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="9" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E18" s="9"/>
       <c r="F18" s="11" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G18" s="11"/>
     </row>
     <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="9" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E19" s="9"/>
       <c r="F19" s="13" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G19" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="9" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E20" s="9"/>
       <c r="F20" s="13" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="9" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E21" s="9"/>
       <c r="F21" s="11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G21" s="11"/>
     </row>
     <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E22" s="9"/>
       <c r="F22" s="13" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G22" s="13"/>
     </row>
     <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="9" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E23" s="9"/>
       <c r="F23" s="11" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G23" s="11"/>
     </row>
     <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="18" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E24" s="18"/>
       <c r="F24" s="13" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G24" s="13"/>
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="18" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E25" s="18"/>
       <c r="F25" s="13" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G25" s="13"/>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -20814,22 +21163,22 @@
     </row>
     <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>7</v>
@@ -20837,143 +21186,143 @@
     </row>
     <row r="29" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="34" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B29" s="35" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D29" s="35" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E29" s="35" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F29" s="36" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="34" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B30" s="35" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C30" s="35" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D30" s="35" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E30" s="35" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="34" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B31" s="35" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C31" s="35" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D31" s="35" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E31" s="35" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G31" s="11"/>
     </row>
     <row r="32" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="38" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B32" s="39" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C32" s="39" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D32" s="39" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E32" s="39" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F32" s="40" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="38" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B33" s="39" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C33" s="39" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D33" s="39" t="s">
+        <v>178</v>
+      </c>
+      <c r="E33" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="F33" s="40" t="s">
         <v>174</v>
       </c>
-      <c r="E33" s="39" t="s">
-        <v>175</v>
-      </c>
-      <c r="F33" s="40" t="s">
-        <v>170</v>
-      </c>
       <c r="G33" s="13" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="34" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B34" s="35" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D34" s="35" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E34" s="35" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="41" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B35" s="41"/>
       <c r="C35" s="41"/>
@@ -20984,7 +21333,7 @@
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -20995,25 +21344,25 @@
     </row>
     <row r="38" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21033,14 +21382,14 @@
         <v>66.375</v>
       </c>
       <c r="E39" s="35" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F39" s="45" t="n">
         <f aca="false">70/(A39*1000/$C$5)</f>
         <v>20.16</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21060,14 +21409,14 @@
         <v>106.2</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="F40" s="45" t="n">
         <f aca="false">70/(A40*1000/$C$5)</f>
         <v>32.256</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21087,14 +21436,14 @@
         <v>132.75</v>
       </c>
       <c r="E41" s="49" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F41" s="50" t="n">
         <f aca="false">70/(A41*1000/$C$5)</f>
         <v>40.32</v>
       </c>
       <c r="G41" s="51" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21114,14 +21463,14 @@
         <v>177</v>
       </c>
       <c r="E42" s="37" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="F42" s="45" t="n">
         <f aca="false">70/(A42*1000/$C$5)</f>
         <v>53.76</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21141,14 +21490,14 @@
         <v>212.4</v>
       </c>
       <c r="E43" s="37" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="F43" s="45" t="n">
         <f aca="false">70/(A43*1000/$C$5)</f>
         <v>64.512</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21168,19 +21517,19 @@
         <v>354</v>
       </c>
       <c r="E44" s="37" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="F44" s="45" t="n">
         <f aca="false">70/(A44*1000/$C$5)</f>
         <v>107.52</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="41" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B45" s="41"/>
       <c r="C45" s="41"/>
@@ -21191,7 +21540,7 @@
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -21205,11 +21554,11 @@
         <v>27</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="5" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="4" t="s">
@@ -21219,7 +21568,7 @@
     </row>
     <row r="49" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B49" s="52" t="n">
         <f aca="false">($C$13/4)</f>
@@ -21232,13 +21581,13 @@
       </c>
       <c r="E49" s="53"/>
       <c r="F49" s="13" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="G49" s="13"/>
     </row>
     <row r="50" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B50" s="54" t="n">
         <f aca="false">($C$9*(1+($C$13/4)))</f>
@@ -21251,13 +21600,13 @@
       </c>
       <c r="E50" s="55"/>
       <c r="F50" s="13" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G50" s="13"/>
     </row>
     <row r="51" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B51" s="56" t="n">
         <f aca="false">(1.22*$C$10/(($C$13/4)/(2*($C$9*(1+($C$13/4))))))</f>
@@ -21270,13 +21619,13 @@
       </c>
       <c r="E51" s="57"/>
       <c r="F51" s="13" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G51" s="13"/>
     </row>
     <row r="52" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B52" s="58" t="n">
         <f aca="false">4*1000/$C$5</f>
@@ -21289,13 +21638,13 @@
       </c>
       <c r="E52" s="59"/>
       <c r="F52" s="11" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G52" s="11"/>
     </row>
     <row r="53" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B53" s="58" t="n">
         <f aca="false">4*1000/$C$5</f>
@@ -21308,30 +21657,30 @@
       </c>
       <c r="E53" s="59"/>
       <c r="F53" s="13" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G53" s="13"/>
     </row>
     <row r="54" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B54" s="60" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C54" s="60"/>
       <c r="D54" s="60" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E54" s="60"/>
       <c r="F54" s="13" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G54" s="13"/>
     </row>
     <row r="56" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -21342,14 +21691,14 @@
     </row>
     <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
@@ -21357,14 +21706,14 @@
     </row>
     <row r="58" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="32" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B58" s="32"/>
       <c r="C58" s="61" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E58" s="11"/>
       <c r="F58" s="11"/>
@@ -21372,14 +21721,14 @@
     </row>
     <row r="59" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="32" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B59" s="32"/>
       <c r="C59" s="61" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E59" s="11"/>
       <c r="F59" s="11"/>
@@ -21387,14 +21736,14 @@
     </row>
     <row r="60" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="29" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B60" s="29"/>
       <c r="C60" s="61" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E60" s="11"/>
       <c r="F60" s="11"/>
@@ -21402,14 +21751,14 @@
     </row>
     <row r="61" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="32" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B61" s="32"/>
       <c r="C61" s="62" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E61" s="11"/>
       <c r="F61" s="11"/>
@@ -21417,7 +21766,7 @@
     </row>
     <row r="63" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="27" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B63" s="27"/>
       <c r="C63" s="27"/>
@@ -21544,7 +21893,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -21555,7 +21904,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -21566,7 +21915,7 @@
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -21580,11 +21929,11 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4" t="s">
@@ -21594,109 +21943,109 @@
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="63" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E6" s="9"/>
       <c r="F6" s="13" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="G6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="63" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="13" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="G7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="64" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C8" s="18"/>
       <c r="D8" s="9" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="11" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="G8" s="11"/>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="63" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C9" s="18"/>
       <c r="D9" s="9" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="13" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="G9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="63" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="13" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="G10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="63" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="E11" s="9"/>
       <c r="F11" s="13" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="G11" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -21707,41 +22056,41 @@
     </row>
     <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="63" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B14" s="63"/>
       <c r="C14" s="30" t="n">
         <v>10</v>
       </c>
       <c r="D14" s="65" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F14" s="13"/>
       <c r="G14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="63" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B15" s="63"/>
       <c r="C15" s="66" t="n">
         <v>0.65</v>
       </c>
       <c r="D15" s="67" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="F15" s="13"/>
       <c r="G15" s="13"/>
     </row>
     <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="63" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B16" s="63"/>
       <c r="C16" s="66" t="n">
@@ -21749,14 +22098,14 @@
       </c>
       <c r="D16" s="65"/>
       <c r="E16" s="13" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="F16" s="13"/>
       <c r="G16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="63" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B17" s="63"/>
       <c r="C17" s="66" t="n">
@@ -21764,82 +22113,82 @@
       </c>
       <c r="D17" s="65"/>
       <c r="E17" s="13" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="F17" s="13"/>
       <c r="G17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="64" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B18" s="64"/>
       <c r="C18" s="30" t="n">
         <v>0.7</v>
       </c>
       <c r="D18" s="65" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="64" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B19" s="64"/>
       <c r="C19" s="30" t="n">
         <v>9248</v>
       </c>
       <c r="D19" s="65" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="63" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B20" s="63"/>
       <c r="C20" s="30" t="n">
         <v>1920</v>
       </c>
       <c r="D20" s="65" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F20" s="11"/>
       <c r="G20" s="11"/>
     </row>
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="64" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B21" s="64"/>
       <c r="C21" s="30" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="67" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="F21" s="13"/>
       <c r="G21" s="13"/>
     </row>
     <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="64" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B22" s="64"/>
       <c r="C22" s="30" t="n">
@@ -21847,82 +22196,82 @@
       </c>
       <c r="D22" s="65"/>
       <c r="E22" s="11" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F22" s="11"/>
       <c r="G22" s="11"/>
     </row>
     <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="64" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B23" s="64"/>
       <c r="C23" s="66" t="n">
         <v>2.2</v>
       </c>
       <c r="D23" s="65" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
     </row>
     <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="64" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B24" s="64"/>
       <c r="C24" s="30" t="n">
         <v>2304</v>
       </c>
       <c r="D24" s="65" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="F24" s="13"/>
       <c r="G24" s="13"/>
     </row>
     <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="63" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B25" s="63"/>
       <c r="C25" s="30" t="n">
         <v>0.55</v>
       </c>
       <c r="D25" s="65" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F25" s="13"/>
       <c r="G25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="63" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B26" s="63"/>
       <c r="C26" s="30" t="n">
         <v>400</v>
       </c>
       <c r="D26" s="65" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F26" s="11"/>
       <c r="G26" s="11"/>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -21933,16 +22282,16 @@
     </row>
     <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>7</v>
@@ -21952,7 +22301,7 @@
     </row>
     <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="63" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B30" s="68" t="n">
         <f aca="false">($C$18/$C$15)</f>
@@ -21967,14 +22316,14 @@
         <v>2.2</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F30" s="13"/>
       <c r="G30" s="13"/>
     </row>
     <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="63" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B31" s="71" t="n">
         <f aca="false">($C$16*(1+$C$15))</f>
@@ -21989,14 +22338,14 @@
         <v>4</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="F31" s="13"/>
       <c r="G31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="63" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B32" s="74" t="n">
         <f aca="false">(2.44*$C$25*($C$16*(1+$C$15))/$C$15)</f>
@@ -22011,14 +22360,14 @@
         <v>5.368</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F32" s="13"/>
       <c r="G32" s="13"/>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="63" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B33" s="77" t="n">
         <f aca="false">(2*$C$16*(2*$C$18)*(1+$C$15)/$C$15^2)</f>
@@ -22033,14 +22382,14 @@
         <v>35.2</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F33" s="13"/>
       <c r="G33" s="13"/>
     </row>
     <row r="34" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="63" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B34" s="80" t="n">
         <f aca="false">($C$20*$C$18/$C$15/1000)</f>
@@ -22055,14 +22404,14 @@
         <v>5.0688</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F34" s="13"/>
       <c r="G34" s="13"/>
     </row>
     <row r="35" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="63" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B35" s="80" t="n">
         <f aca="false">($C$19*$C$18/$C$15/1000)</f>
@@ -22077,14 +22426,14 @@
         <v>5.0688</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="F35" s="13"/>
       <c r="G35" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="63" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B36" s="83" t="n">
         <f aca="false">70/($C$18/$C$15)</f>
@@ -22099,14 +22448,14 @@
         <v>31.8181818181818</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F36" s="13"/>
       <c r="G36" s="13"/>
     </row>
     <row r="37" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="63" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B37" s="86" t="n">
         <f aca="false">$C$26/($C$20*$C$18/$C$15/1000)</f>
@@ -22121,14 +22470,14 @@
         <v>78.9141414141414</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F37" s="11"/>
       <c r="G37" s="11"/>
     </row>
     <row r="38" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="89" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B38" s="89"/>
       <c r="C38" s="89"/>
@@ -22139,7 +22488,7 @@
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -22150,26 +22499,26 @@
     </row>
     <row r="41" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="64" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B42" s="90" t="n">
         <f aca="false">($C$18/$C$15)</f>
@@ -22184,14 +22533,14 @@
         <v>2.15384615384615</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="F42" s="13"/>
       <c r="G42" s="13"/>
     </row>
     <row r="43" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="64" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B43" s="93" t="n">
         <f aca="false">2*$C$18/$C$15</f>
@@ -22206,14 +22555,14 @@
         <v>4.30769230769231</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F43" s="13"/>
       <c r="G43" s="13"/>
     </row>
     <row r="44" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="64" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B44" s="90" t="n">
         <f aca="false">($C$19*$C$18/$C$15/1000)/$C$20/0.001</f>
@@ -22228,14 +22577,14 @@
         <v>10.374358974359</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="F44" s="13"/>
       <c r="G44" s="13"/>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -22249,13 +22598,13 @@
         <v>27</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>7</v>
@@ -22265,16 +22614,16 @@
     </row>
     <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="63" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B48" s="96" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C48" s="97" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D48" s="98" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
@@ -22282,16 +22631,16 @@
     </row>
     <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="63" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B49" s="96" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C49" s="97" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D49" s="99" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
@@ -22299,197 +22648,197 @@
     </row>
     <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="100" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B50" s="101" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C50" s="101" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D50" s="102" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="E50" s="103" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F50" s="103"/>
       <c r="G50" s="103"/>
     </row>
     <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="104" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B51" s="102" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C51" s="102" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D51" s="102" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="E51" s="103" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="F51" s="103"/>
       <c r="G51" s="103"/>
     </row>
     <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="100" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B52" s="102" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C52" s="102" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D52" s="102" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="E52" s="103" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="F52" s="103"/>
       <c r="G52" s="103"/>
     </row>
     <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="63" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B53" s="96" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C53" s="105" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D53" s="98" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F53" s="13"/>
       <c r="G53" s="13"/>
     </row>
     <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="63" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B54" s="96" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C54" s="105" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D54" s="98" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F54" s="13"/>
       <c r="G54" s="13"/>
     </row>
     <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="63" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B55" s="96" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C55" s="105" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D55" s="98" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F55" s="11"/>
       <c r="G55" s="11"/>
     </row>
     <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="100" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B56" s="101" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C56" s="101" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D56" s="101" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E56" s="106" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F56" s="106"/>
       <c r="G56" s="106"/>
     </row>
     <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="63" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B57" s="96" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C57" s="97" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D57" s="98" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F57" s="11"/>
       <c r="G57" s="11"/>
     </row>
     <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="64" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B58" s="96" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C58" s="105" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D58" s="98" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F58" s="13"/>
       <c r="G58" s="13"/>
     </row>
     <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="63" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B59" s="107" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C59" s="105" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D59" s="99" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F59" s="13"/>
       <c r="G59" s="13"/>
     </row>
     <row r="61" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -22500,11 +22849,11 @@
     </row>
     <row r="62" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="108" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B62" s="108"/>
       <c r="C62" s="13" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="D62" s="13"/>
       <c r="E62" s="13"/>
@@ -22513,11 +22862,11 @@
     </row>
     <row r="63" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="108" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B63" s="108"/>
       <c r="C63" s="13" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D63" s="13"/>
       <c r="E63" s="13"/>
@@ -22526,11 +22875,11 @@
     </row>
     <row r="64" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="108" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B64" s="108"/>
       <c r="C64" s="13" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D64" s="13"/>
       <c r="E64" s="13"/>
@@ -22539,11 +22888,11 @@
     </row>
     <row r="65" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="108" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B65" s="108"/>
       <c r="C65" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="D65" s="13"/>
       <c r="E65" s="13"/>
@@ -22552,11 +22901,11 @@
     </row>
     <row r="66" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="108" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B66" s="108"/>
       <c r="C66" s="13" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D66" s="13"/>
       <c r="E66" s="13"/>
@@ -22565,7 +22914,7 @@
     </row>
     <row r="68" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="27" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B68" s="27"/>
       <c r="C68" s="27"/>
@@ -22696,7 +23045,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -22707,7 +23056,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -22718,7 +23067,7 @@
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -22732,11 +23081,11 @@
         <v>27</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="4" t="s">
@@ -22746,75 +23095,75 @@
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C6" s="19"/>
       <c r="D6" s="18" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="E6" s="18"/>
       <c r="F6" s="11" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="G6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C7" s="19"/>
       <c r="D7" s="18" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E7" s="18"/>
       <c r="F7" s="13" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="G7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="18" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="E8" s="18"/>
       <c r="F8" s="13" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="G8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C9" s="19"/>
       <c r="D9" s="9" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="13" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="G9" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -22828,11 +23177,11 @@
         <v>27</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="4" t="s">
@@ -22842,58 +23191,58 @@
     </row>
     <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C13" s="19"/>
       <c r="D13" s="9" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="13" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="G13" s="13"/>
     </row>
     <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C14" s="19"/>
       <c r="D14" s="9" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="E14" s="9"/>
       <c r="F14" s="13" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="G14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C15" s="19"/>
       <c r="D15" s="18" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E15" s="18"/>
       <c r="F15" s="13" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="G15" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -22907,11 +23256,11 @@
         <v>27</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="4" t="s">
@@ -22921,65 +23270,65 @@
     </row>
     <row r="19" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C19" s="19"/>
       <c r="D19" s="18" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E19" s="18"/>
       <c r="F19" s="13" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="G19" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C20" s="19"/>
       <c r="D20" s="9" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E20" s="9"/>
       <c r="F20" s="13" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="G20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C21" s="19"/>
       <c r="D21" s="18" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E21" s="18"/>
       <c r="F21" s="13" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="G21" s="13"/>
     </row>
     <row r="22" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C22" s="19"/>
       <c r="D22" s="9" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E22" s="9"/>
       <c r="F22" s="11"/>
@@ -22987,7 +23336,7 @@
     </row>
     <row r="23" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="89" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B23" s="89"/>
       <c r="C23" s="89"/>
@@ -22998,7 +23347,7 @@
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -23009,51 +23358,51 @@
     </row>
     <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="109" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B26" s="110" t="n">
         <v>2400</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D26" s="110" t="n">
         <v>2483.5</v>
       </c>
       <c r="E26" s="35" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="F26" s="111" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="G26" s="111"/>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="109" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B28" s="112" t="n">
         <v>533</v>
@@ -23081,7 +23430,7 @@
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="109" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="B29" s="112" t="n">
         <v>666.5</v>
@@ -23109,7 +23458,7 @@
     </row>
     <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="113" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B30" s="114" t="n">
         <v>800</v>
@@ -23137,7 +23486,7 @@
     </row>
     <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="109" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B31" s="112" t="n">
         <v>933</v>
@@ -23165,7 +23514,7 @@
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="109" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B32" s="112" t="n">
         <v>1066.5</v>
@@ -23193,7 +23542,7 @@
     </row>
     <row r="33" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="116" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B33" s="116"/>
       <c r="C33" s="116"/>
@@ -23207,11 +23556,11 @@
         <v>27</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="5" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="4" t="s">
@@ -23221,41 +23570,41 @@
     </row>
     <row r="36" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C36" s="19"/>
       <c r="D36" s="18" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="E36" s="18"/>
       <c r="F36" s="11" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="G36" s="11"/>
     </row>
     <row r="37" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C37" s="19"/>
       <c r="D37" s="18" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E37" s="18"/>
       <c r="F37" s="13" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G37" s="13"/>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -23269,11 +23618,11 @@
         <v>27</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="4" t="s">
@@ -23283,75 +23632,75 @@
     </row>
     <row r="41" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="9" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E41" s="9"/>
       <c r="F41" s="11" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="G41" s="11"/>
     </row>
     <row r="42" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C42" s="19"/>
       <c r="D42" s="18" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="E42" s="18"/>
       <c r="F42" s="13" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="G42" s="13"/>
     </row>
     <row r="43" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C43" s="19"/>
       <c r="D43" s="18" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E43" s="18"/>
       <c r="F43" s="13" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="G43" s="13"/>
     </row>
     <row r="44" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C44" s="19"/>
       <c r="D44" s="9" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="E44" s="9"/>
       <c r="F44" s="13" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="G44" s="13"/>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -23362,11 +23711,11 @@
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="108" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B47" s="108"/>
       <c r="C47" s="13" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="D47" s="13"/>
       <c r="E47" s="13"/>
@@ -23375,11 +23724,11 @@
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="108" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B48" s="108"/>
       <c r="C48" s="11" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D48" s="11"/>
       <c r="E48" s="11"/>
@@ -23388,11 +23737,11 @@
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="108" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B49" s="108"/>
       <c r="C49" s="11" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="D49" s="11"/>
       <c r="E49" s="11"/>
@@ -23401,11 +23750,11 @@
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="108" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B50" s="108"/>
       <c r="C50" s="11" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="D50" s="11"/>
       <c r="E50" s="11"/>
@@ -23414,11 +23763,11 @@
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="108" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B51" s="108"/>
       <c r="C51" s="11" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="D51" s="11"/>
       <c r="E51" s="11"/>
@@ -23427,7 +23776,7 @@
     </row>
     <row r="53" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="27" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B53" s="27"/>
       <c r="C53" s="27"/>
@@ -23552,7 +23901,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="117" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B1" s="117"/>
       <c r="C1" s="117"/>
@@ -23563,27 +23912,27 @@
         <v>3</v>
       </c>
       <c r="B3" s="119" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C3" s="119" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="D3" s="118" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="120" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B4" s="121" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C4" s="121" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="D4" s="121" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23591,69 +23940,69 @@
         <v>12</v>
       </c>
       <c r="B5" s="121" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C5" s="121" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="D5" s="121" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="120" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B6" s="121" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C6" s="121" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="D6" s="120" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="120" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B7" s="121" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C7" s="121" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D7" s="121" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="120" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B8" s="121" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C8" s="120" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="D8" s="121" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="120" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B9" s="120" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C9" s="121" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="D9" s="121" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
   </sheetData>
